--- a/VanHanhCD1/wwwroot/templates/BMVH_LoVoiDung2.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_LoVoiDung2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CEDB20-3A0E-4E22-9A4D-A9D15FC0BB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D75B1EB-21C0-4D75-B2F8-72BBA0999F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="578" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="578" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -18,17 +18,26 @@
     <sheet name="Ca Ngay" sheetId="3" r:id="rId3"/>
     <sheet name="Ca Dem" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="265">
   <si>
     <t>BM.04/QT.05.04</t>
   </si>
@@ -1414,7 +1423,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1634,47 +1643,155 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1721,167 +1838,65 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1901,19 +1916,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1922,41 +1928,17 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="18" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1991,6 +1973,33 @@
     <xf numFmtId="1" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="16" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2001,9 +2010,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2054,7 +2060,7 @@
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
           <a:off x="38729" y="87974"/>
-          <a:ext cx="3390271" cy="290184"/>
+          <a:ext cx="3390271" cy="287803"/>
           <a:chOff x="162" y="-2299"/>
           <a:chExt cx="21092" cy="6018"/>
         </a:xfrm>
@@ -2588,22 +2594,22 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="126"/>
-      <c r="U3" s="126"/>
-      <c r="V3" s="126"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="121"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="121"/>
+      <c r="U3" s="121"/>
+      <c r="V3" s="121"/>
     </row>
     <row r="4" spans="1:223" ht="21" customHeight="1">
       <c r="A4" s="8"/>
@@ -2611,19 +2617,19 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="127" t="s">
+      <c r="F4" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="127"/>
-      <c r="P4" s="127"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
@@ -2638,33 +2644,33 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="129"/>
-      <c r="K5" s="129"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="129"/>
-      <c r="O5" s="129"/>
-      <c r="P5" s="129"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="129"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="129"/>
-      <c r="U5" s="129"/>
-      <c r="V5" s="129"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="124"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="124"/>
     </row>
     <row r="6" spans="1:223" s="17" customFormat="1" ht="69" customHeight="1">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="130" t="s">
+      <c r="B6" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="132"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
       <c r="F6" s="10" t="s">
         <v>5</v>
       </c>
@@ -2739,14 +2745,14 @@
       </c>
     </row>
     <row r="7" spans="1:223" s="1" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A7" s="153" t="s">
+      <c r="A7" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="135"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="103"/>
       <c r="E7" s="19">
         <v>5404</v>
       </c>
@@ -3042,10 +3048,10 @@
       <c r="HO7" s="3"/>
     </row>
     <row r="8" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A8" s="94"/>
-      <c r="B8" s="139"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="141"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
       <c r="E8" s="19">
         <v>5408</v>
       </c>
@@ -3147,10 +3153,10 @@
       </c>
     </row>
     <row r="9" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A9" s="94"/>
-      <c r="B9" s="139"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="141"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="106"/>
       <c r="E9" s="19">
         <v>5414</v>
       </c>
@@ -3252,10 +3258,10 @@
       </c>
     </row>
     <row r="10" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="136"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="138"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="109"/>
       <c r="E10" s="19">
         <v>5418</v>
       </c>
@@ -3357,12 +3363,12 @@
       </c>
     </row>
     <row r="11" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="133" t="s">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="135"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="103"/>
       <c r="E11" s="19">
         <v>4405</v>
       </c>
@@ -3464,10 +3470,10 @@
       </c>
     </row>
     <row r="12" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="141"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="19">
         <v>4412</v>
       </c>
@@ -3569,10 +3575,10 @@
       </c>
     </row>
     <row r="13" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="136"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="138"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
       <c r="E13" s="19">
         <v>4420</v>
       </c>
@@ -3674,12 +3680,12 @@
       </c>
     </row>
     <row r="14" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="133" t="s">
+      <c r="A14" s="100"/>
+      <c r="B14" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="135"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="103"/>
       <c r="E14" s="19">
         <v>4402</v>
       </c>
@@ -3781,10 +3787,10 @@
       </c>
     </row>
     <row r="15" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="139"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="141"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="19">
         <v>4405</v>
       </c>
@@ -3886,10 +3892,10 @@
       </c>
     </row>
     <row r="16" spans="1:223" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="139"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="141"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="106"/>
       <c r="E16" s="19">
         <v>4409</v>
       </c>
@@ -3991,10 +3997,10 @@
       </c>
     </row>
     <row r="17" spans="1:29" s="2" customFormat="1" ht="16.5">
-      <c r="A17" s="94"/>
-      <c r="B17" s="139"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="141"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="104"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="106"/>
       <c r="E17" s="19">
         <v>4412</v>
       </c>
@@ -4096,10 +4102,10 @@
       </c>
     </row>
     <row r="18" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="139"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="141"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="104"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="106"/>
       <c r="E18" s="19">
         <v>4415</v>
       </c>
@@ -4201,10 +4207,10 @@
       </c>
     </row>
     <row r="19" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A19" s="94"/>
-      <c r="B19" s="139"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="141"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="16">
         <v>4419</v>
       </c>
@@ -4306,12 +4312,12 @@
       </c>
     </row>
     <row r="20" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A20" s="94"/>
-      <c r="B20" s="133" t="s">
+      <c r="A20" s="100"/>
+      <c r="B20" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="134"/>
-      <c r="D20" s="135"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="103"/>
       <c r="E20" s="19">
         <v>3201</v>
       </c>
@@ -4413,10 +4419,10 @@
       </c>
     </row>
     <row r="21" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A21" s="94"/>
-      <c r="B21" s="139"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="141"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="106"/>
       <c r="E21" s="19">
         <v>3203</v>
       </c>
@@ -4518,10 +4524,10 @@
       </c>
     </row>
     <row r="22" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A22" s="94"/>
-      <c r="B22" s="139"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="141"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="104"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="106"/>
       <c r="E22" s="17">
         <v>3206</v>
       </c>
@@ -4623,10 +4629,10 @@
       </c>
     </row>
     <row r="23" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="106"/>
       <c r="E23" s="19">
         <v>3208</v>
       </c>
@@ -4728,10 +4734,10 @@
       </c>
     </row>
     <row r="24" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A24" s="94"/>
-      <c r="B24" s="139"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="141"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="106"/>
       <c r="E24" s="19">
         <v>3211</v>
       </c>
@@ -4833,10 +4839,10 @@
       </c>
     </row>
     <row r="25" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A25" s="94"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="141"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="106"/>
       <c r="E25" s="19">
         <v>3213</v>
       </c>
@@ -4938,10 +4944,10 @@
       </c>
     </row>
     <row r="26" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A26" s="94"/>
-      <c r="B26" s="139"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="141"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="106"/>
       <c r="E26" s="19">
         <v>3216</v>
       </c>
@@ -5043,10 +5049,10 @@
       </c>
     </row>
     <row r="27" spans="1:29" s="2" customFormat="1" ht="16.5">
-      <c r="A27" s="94"/>
-      <c r="B27" s="136"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="138"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
       <c r="E27" s="19">
         <v>3218</v>
       </c>
@@ -5148,12 +5154,12 @@
       </c>
     </row>
     <row r="28" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="133" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="134"/>
-      <c r="D28" s="135"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103"/>
       <c r="E28" s="19">
         <v>1808</v>
       </c>
@@ -5255,10 +5261,10 @@
       </c>
     </row>
     <row r="29" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A29" s="94"/>
-      <c r="B29" s="136"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="138"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="107"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109"/>
       <c r="E29" s="19">
         <v>1818</v>
       </c>
@@ -5360,12 +5366,12 @@
       </c>
     </row>
     <row r="30" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A30" s="94"/>
-      <c r="B30" s="133" t="s">
+      <c r="A30" s="100"/>
+      <c r="B30" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="135"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
       <c r="E30" s="19">
         <v>1403</v>
       </c>
@@ -5467,10 +5473,10 @@
       </c>
     </row>
     <row r="31" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A31" s="94"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="141"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="106"/>
       <c r="E31" s="19">
         <v>1408</v>
       </c>
@@ -5572,10 +5578,10 @@
       </c>
     </row>
     <row r="32" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A32" s="94"/>
-      <c r="B32" s="139"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="141"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="106"/>
       <c r="E32" s="19">
         <v>1413</v>
       </c>
@@ -5677,10 +5683,10 @@
       </c>
     </row>
     <row r="33" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A33" s="94"/>
-      <c r="B33" s="136"/>
-      <c r="C33" s="137"/>
-      <c r="D33" s="138"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="109"/>
       <c r="E33" s="19">
         <v>1418</v>
       </c>
@@ -5782,12 +5788,12 @@
       </c>
     </row>
     <row r="34" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A34" s="94"/>
-      <c r="B34" s="145" t="s">
+      <c r="A34" s="100"/>
+      <c r="B34" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="146"/>
-      <c r="D34" s="147"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="96"/>
       <c r="E34" s="19">
         <v>4311</v>
       </c>
@@ -5889,11 +5895,11 @@
       </c>
     </row>
     <row r="35" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A35" s="94"/>
-      <c r="B35" s="119" t="s">
+      <c r="A35" s="100"/>
+      <c r="B35" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="120"/>
+      <c r="C35" s="112"/>
       <c r="D35" s="13" t="s">
         <v>38</v>
       </c>
@@ -5996,9 +6002,9 @@
       </c>
     </row>
     <row r="36" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A36" s="94"/>
-      <c r="B36" s="121"/>
-      <c r="C36" s="122"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="113"/>
+      <c r="C36" s="114"/>
       <c r="D36" s="13" t="s">
         <v>39</v>
       </c>
@@ -6101,9 +6107,9 @@
       </c>
     </row>
     <row r="37" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A37" s="94"/>
-      <c r="B37" s="123"/>
-      <c r="C37" s="124"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="13" t="s">
         <v>40</v>
       </c>
@@ -6206,12 +6212,12 @@
       </c>
     </row>
     <row r="38" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A38" s="94"/>
-      <c r="B38" s="116" t="s">
+      <c r="A38" s="100"/>
+      <c r="B38" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="117"/>
-      <c r="D38" s="118"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
       <c r="E38" s="19"/>
       <c r="F38" s="25">
         <f>Sheet2!E37</f>
@@ -6311,11 +6317,11 @@
       </c>
     </row>
     <row r="39" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A39" s="94"/>
-      <c r="B39" s="125" t="s">
+      <c r="A39" s="100"/>
+      <c r="B39" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="125"/>
+      <c r="C39" s="110"/>
       <c r="D39" s="15" t="s">
         <v>43</v>
       </c>
@@ -6420,9 +6426,9 @@
       </c>
     </row>
     <row r="40" spans="1:29" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A40" s="94"/>
-      <c r="B40" s="125"/>
-      <c r="C40" s="125"/>
+      <c r="A40" s="100"/>
+      <c r="B40" s="110"/>
+      <c r="C40" s="110"/>
       <c r="D40" s="15" t="s">
         <v>45</v>
       </c>
@@ -6527,14 +6533,14 @@
       </c>
     </row>
     <row r="41" spans="1:29" s="51" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A41" s="94" t="s">
+      <c r="A41" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="154" t="s">
+      <c r="B41" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="154"/>
-      <c r="D41" s="154"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
       <c r="E41" s="50" t="s">
         <v>49</v>
       </c>
@@ -6636,12 +6642,12 @@
       </c>
     </row>
     <row r="42" spans="1:29" s="17" customFormat="1" ht="16.5">
-      <c r="A42" s="94"/>
-      <c r="B42" s="125" t="s">
+      <c r="A42" s="100"/>
+      <c r="B42" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="125"/>
-      <c r="D42" s="125"/>
+      <c r="C42" s="110"/>
+      <c r="D42" s="110"/>
       <c r="E42" s="22" t="s">
         <v>51</v>
       </c>
@@ -6743,12 +6749,12 @@
       </c>
     </row>
     <row r="43" spans="1:29" ht="16.5">
-      <c r="A43" s="94"/>
-      <c r="B43" s="125" t="s">
+      <c r="A43" s="100"/>
+      <c r="B43" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="125"/>
-      <c r="D43" s="125"/>
+      <c r="C43" s="110"/>
+      <c r="D43" s="110"/>
       <c r="E43" s="22" t="s">
         <v>53</v>
       </c>
@@ -6850,12 +6856,12 @@
       </c>
     </row>
     <row r="44" spans="1:29" ht="16.5">
-      <c r="A44" s="94"/>
-      <c r="B44" s="125" t="s">
+      <c r="A44" s="100"/>
+      <c r="B44" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="125"/>
-      <c r="D44" s="125"/>
+      <c r="C44" s="110"/>
+      <c r="D44" s="110"/>
       <c r="E44" s="22" t="s">
         <v>55</v>
       </c>
@@ -6957,12 +6963,12 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="16.5">
-      <c r="A45" s="94"/>
-      <c r="B45" s="125" t="s">
+      <c r="A45" s="100"/>
+      <c r="B45" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="125"/>
-      <c r="D45" s="125"/>
+      <c r="C45" s="110"/>
+      <c r="D45" s="110"/>
       <c r="E45" s="22" t="s">
         <v>57</v>
       </c>
@@ -7064,12 +7070,12 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="16.5">
-      <c r="A46" s="94"/>
-      <c r="B46" s="125" t="s">
+      <c r="A46" s="100"/>
+      <c r="B46" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="125"/>
-      <c r="D46" s="125"/>
+      <c r="C46" s="110"/>
+      <c r="D46" s="110"/>
       <c r="E46" s="22" t="s">
         <v>59</v>
       </c>
@@ -7171,12 +7177,12 @@
       </c>
     </row>
     <row r="47" spans="1:29" ht="16.5">
-      <c r="A47" s="94"/>
-      <c r="B47" s="125" t="s">
+      <c r="A47" s="100"/>
+      <c r="B47" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="125"/>
-      <c r="D47" s="125"/>
+      <c r="C47" s="110"/>
+      <c r="D47" s="110"/>
       <c r="E47" s="22" t="s">
         <v>61</v>
       </c>
@@ -7278,12 +7284,12 @@
       </c>
     </row>
     <row r="48" spans="1:29" ht="16.5">
-      <c r="A48" s="94"/>
-      <c r="B48" s="125" t="s">
+      <c r="A48" s="100"/>
+      <c r="B48" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="125"/>
-      <c r="D48" s="125"/>
+      <c r="C48" s="110"/>
+      <c r="D48" s="110"/>
       <c r="E48" s="22" t="s">
         <v>63</v>
       </c>
@@ -7385,12 +7391,12 @@
       </c>
     </row>
     <row r="49" spans="1:29" ht="16.5">
-      <c r="A49" s="94"/>
-      <c r="B49" s="125" t="s">
+      <c r="A49" s="100"/>
+      <c r="B49" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="125"/>
-      <c r="D49" s="125"/>
+      <c r="C49" s="110"/>
+      <c r="D49" s="110"/>
       <c r="E49" s="22" t="s">
         <v>65</v>
       </c>
@@ -7492,12 +7498,12 @@
       </c>
     </row>
     <row r="50" spans="1:29" ht="16.5">
-      <c r="A50" s="94"/>
-      <c r="B50" s="125" t="s">
+      <c r="A50" s="100"/>
+      <c r="B50" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="125"/>
-      <c r="D50" s="125"/>
+      <c r="C50" s="110"/>
+      <c r="D50" s="110"/>
       <c r="E50" s="22" t="s">
         <v>67</v>
       </c>
@@ -7599,12 +7605,12 @@
       </c>
     </row>
     <row r="51" spans="1:29" ht="16.5">
-      <c r="A51" s="94"/>
-      <c r="B51" s="125" t="s">
+      <c r="A51" s="100"/>
+      <c r="B51" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="125"/>
-      <c r="D51" s="125"/>
+      <c r="C51" s="110"/>
+      <c r="D51" s="110"/>
       <c r="E51" s="22" t="s">
         <v>69</v>
       </c>
@@ -7706,12 +7712,12 @@
       </c>
     </row>
     <row r="52" spans="1:29" ht="16.5">
-      <c r="A52" s="94"/>
-      <c r="B52" s="125" t="s">
+      <c r="A52" s="100"/>
+      <c r="B52" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="125"/>
-      <c r="D52" s="125"/>
+      <c r="C52" s="110"/>
+      <c r="D52" s="110"/>
       <c r="E52" s="22" t="s">
         <v>71</v>
       </c>
@@ -7813,12 +7819,12 @@
       </c>
     </row>
     <row r="53" spans="1:29" ht="16.5">
-      <c r="A53" s="94"/>
-      <c r="B53" s="125" t="s">
+      <c r="A53" s="100"/>
+      <c r="B53" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="C53" s="125"/>
-      <c r="D53" s="125"/>
+      <c r="C53" s="110"/>
+      <c r="D53" s="110"/>
       <c r="E53" s="21" t="s">
         <v>73</v>
       </c>
@@ -7920,12 +7926,12 @@
       </c>
     </row>
     <row r="54" spans="1:29" ht="16.5">
-      <c r="A54" s="94"/>
-      <c r="B54" s="125" t="s">
+      <c r="A54" s="100"/>
+      <c r="B54" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="125"/>
-      <c r="D54" s="125"/>
+      <c r="C54" s="110"/>
+      <c r="D54" s="110"/>
       <c r="E54" s="22" t="s">
         <v>75</v>
       </c>
@@ -8027,12 +8033,12 @@
       </c>
     </row>
     <row r="55" spans="1:29" ht="16.5">
-      <c r="A55" s="94"/>
-      <c r="B55" s="125" t="s">
+      <c r="A55" s="100"/>
+      <c r="B55" s="110" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="125"/>
-      <c r="D55" s="125"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="110"/>
       <c r="E55" s="22" t="s">
         <v>77</v>
       </c>
@@ -8134,12 +8140,12 @@
       </c>
     </row>
     <row r="56" spans="1:29" ht="16.5">
-      <c r="A56" s="94"/>
-      <c r="B56" s="125" t="s">
+      <c r="A56" s="100"/>
+      <c r="B56" s="110" t="s">
         <v>78</v>
       </c>
-      <c r="C56" s="125"/>
-      <c r="D56" s="125"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="110"/>
       <c r="E56" s="22" t="s">
         <v>79</v>
       </c>
@@ -8241,12 +8247,12 @@
       </c>
     </row>
     <row r="57" spans="1:29" ht="16.5">
-      <c r="A57" s="94"/>
-      <c r="B57" s="125" t="s">
+      <c r="A57" s="100"/>
+      <c r="B57" s="110" t="s">
         <v>80</v>
       </c>
-      <c r="C57" s="125"/>
-      <c r="D57" s="125"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="110"/>
       <c r="E57" s="17" t="s">
         <v>81</v>
       </c>
@@ -8348,12 +8354,12 @@
       </c>
     </row>
     <row r="58" spans="1:29" ht="16.5">
-      <c r="A58" s="94"/>
-      <c r="B58" s="125" t="s">
+      <c r="A58" s="100"/>
+      <c r="B58" s="110" t="s">
         <v>82</v>
       </c>
-      <c r="C58" s="125"/>
-      <c r="D58" s="125"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="110"/>
       <c r="E58" s="22" t="s">
         <v>83</v>
       </c>
@@ -8455,12 +8461,12 @@
       </c>
     </row>
     <row r="59" spans="1:29" ht="16.5">
-      <c r="A59" s="94"/>
-      <c r="B59" s="125" t="s">
+      <c r="A59" s="100"/>
+      <c r="B59" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="C59" s="125"/>
-      <c r="D59" s="125"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="110"/>
       <c r="E59" s="22" t="s">
         <v>85</v>
       </c>
@@ -8562,14 +8568,14 @@
       </c>
     </row>
     <row r="60" spans="1:29" ht="16.5">
-      <c r="A60" s="94" t="s">
+      <c r="A60" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="B60" s="116" t="s">
+      <c r="B60" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="C60" s="117"/>
-      <c r="D60" s="118"/>
+      <c r="C60" s="118"/>
+      <c r="D60" s="119"/>
       <c r="E60" s="21" t="s">
         <v>88</v>
       </c>
@@ -8671,12 +8677,12 @@
       </c>
     </row>
     <row r="61" spans="1:29" ht="16.5">
-      <c r="A61" s="94"/>
-      <c r="B61" s="116" t="s">
+      <c r="A61" s="100"/>
+      <c r="B61" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="117"/>
-      <c r="D61" s="118"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="119"/>
       <c r="E61" s="21" t="s">
         <v>90</v>
       </c>
@@ -8778,12 +8784,12 @@
       </c>
     </row>
     <row r="62" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A62" s="94"/>
-      <c r="B62" s="116" t="s">
+      <c r="A62" s="100"/>
+      <c r="B62" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C62" s="117"/>
-      <c r="D62" s="118"/>
+      <c r="C62" s="118"/>
+      <c r="D62" s="119"/>
       <c r="E62" s="21" t="s">
         <v>92</v>
       </c>
@@ -8885,12 +8891,12 @@
       </c>
     </row>
     <row r="63" spans="1:29" ht="16.5">
-      <c r="A63" s="94"/>
-      <c r="B63" s="116" t="s">
+      <c r="A63" s="100"/>
+      <c r="B63" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="C63" s="117"/>
-      <c r="D63" s="118"/>
+      <c r="C63" s="118"/>
+      <c r="D63" s="119"/>
       <c r="E63" s="21" t="s">
         <v>94</v>
       </c>
@@ -8992,12 +8998,12 @@
       </c>
     </row>
     <row r="64" spans="1:29" ht="16.5">
-      <c r="A64" s="94"/>
-      <c r="B64" s="116" t="s">
+      <c r="A64" s="100"/>
+      <c r="B64" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="117"/>
-      <c r="D64" s="118"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="119"/>
       <c r="E64" s="21" t="s">
         <v>96</v>
       </c>
@@ -9099,12 +9105,12 @@
       </c>
     </row>
     <row r="65" spans="1:29" ht="16.5">
-      <c r="A65" s="94"/>
-      <c r="B65" s="116" t="s">
+      <c r="A65" s="100"/>
+      <c r="B65" s="117" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="117"/>
-      <c r="D65" s="118"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="119"/>
       <c r="E65" s="21" t="s">
         <v>98</v>
       </c>
@@ -9206,12 +9212,12 @@
       </c>
     </row>
     <row r="66" spans="1:29" ht="16.5">
-      <c r="A66" s="94"/>
-      <c r="B66" s="116" t="s">
+      <c r="A66" s="100"/>
+      <c r="B66" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="117"/>
-      <c r="D66" s="118"/>
+      <c r="C66" s="118"/>
+      <c r="D66" s="119"/>
       <c r="E66" s="21" t="s">
         <v>100</v>
       </c>
@@ -9313,12 +9319,12 @@
       </c>
     </row>
     <row r="67" spans="1:29" ht="16.5">
-      <c r="A67" s="94"/>
-      <c r="B67" s="116" t="s">
+      <c r="A67" s="100"/>
+      <c r="B67" s="117" t="s">
         <v>101</v>
       </c>
-      <c r="C67" s="117"/>
-      <c r="D67" s="118"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="119"/>
       <c r="E67" s="21" t="s">
         <v>102</v>
       </c>
@@ -9420,12 +9426,12 @@
       </c>
     </row>
     <row r="68" spans="1:29" ht="16.5">
-      <c r="A68" s="94"/>
-      <c r="B68" s="116" t="s">
+      <c r="A68" s="100"/>
+      <c r="B68" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="C68" s="117"/>
-      <c r="D68" s="118"/>
+      <c r="C68" s="118"/>
+      <c r="D68" s="119"/>
       <c r="E68" s="21" t="s">
         <v>104</v>
       </c>
@@ -9527,12 +9533,12 @@
       </c>
     </row>
     <row r="69" spans="1:29" ht="16.5">
-      <c r="A69" s="94"/>
-      <c r="B69" s="116" t="s">
+      <c r="A69" s="100"/>
+      <c r="B69" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="C69" s="117"/>
-      <c r="D69" s="118"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="119"/>
       <c r="E69" s="21" t="s">
         <v>106</v>
       </c>
@@ -9634,11 +9640,11 @@
       </c>
     </row>
     <row r="70" spans="1:29" ht="16.5">
-      <c r="A70" s="94"/>
-      <c r="B70" s="119" t="s">
+      <c r="A70" s="100"/>
+      <c r="B70" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="C70" s="120"/>
+      <c r="C70" s="112"/>
       <c r="D70" s="18">
         <v>1603</v>
       </c>
@@ -9743,9 +9749,9 @@
       </c>
     </row>
     <row r="71" spans="1:29" ht="16.5">
-      <c r="A71" s="94"/>
-      <c r="B71" s="121"/>
-      <c r="C71" s="122"/>
+      <c r="A71" s="100"/>
+      <c r="B71" s="113"/>
+      <c r="C71" s="114"/>
       <c r="D71" s="18">
         <v>1608</v>
       </c>
@@ -9850,9 +9856,9 @@
       </c>
     </row>
     <row r="72" spans="1:29" ht="16.5">
-      <c r="A72" s="94"/>
-      <c r="B72" s="121"/>
-      <c r="C72" s="122"/>
+      <c r="A72" s="100"/>
+      <c r="B72" s="113"/>
+      <c r="C72" s="114"/>
       <c r="D72" s="18">
         <v>1613</v>
       </c>
@@ -9957,9 +9963,9 @@
       </c>
     </row>
     <row r="73" spans="1:29" ht="16.5">
-      <c r="A73" s="94"/>
-      <c r="B73" s="123"/>
-      <c r="C73" s="124"/>
+      <c r="A73" s="100"/>
+      <c r="B73" s="115"/>
+      <c r="C73" s="116"/>
       <c r="D73" s="18">
         <v>1618</v>
       </c>
@@ -10064,11 +10070,11 @@
       </c>
     </row>
     <row r="74" spans="1:29" ht="16.5">
-      <c r="A74" s="94"/>
-      <c r="B74" s="119" t="s">
+      <c r="A74" s="100"/>
+      <c r="B74" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="C74" s="120"/>
+      <c r="C74" s="112"/>
       <c r="D74" s="18">
         <v>1603</v>
       </c>
@@ -10173,9 +10179,9 @@
       </c>
     </row>
     <row r="75" spans="1:29" ht="16.5">
-      <c r="A75" s="94"/>
-      <c r="B75" s="121"/>
-      <c r="C75" s="122"/>
+      <c r="A75" s="100"/>
+      <c r="B75" s="113"/>
+      <c r="C75" s="114"/>
       <c r="D75" s="18">
         <v>1608</v>
       </c>
@@ -10280,9 +10286,9 @@
       </c>
     </row>
     <row r="76" spans="1:29" ht="16.5">
-      <c r="A76" s="94"/>
-      <c r="B76" s="121"/>
-      <c r="C76" s="122"/>
+      <c r="A76" s="100"/>
+      <c r="B76" s="113"/>
+      <c r="C76" s="114"/>
       <c r="D76" s="18">
         <v>1613</v>
       </c>
@@ -10387,9 +10393,9 @@
       </c>
     </row>
     <row r="77" spans="1:29" ht="16.5">
-      <c r="A77" s="94"/>
-      <c r="B77" s="123"/>
-      <c r="C77" s="124"/>
+      <c r="A77" s="100"/>
+      <c r="B77" s="115"/>
+      <c r="C77" s="116"/>
       <c r="D77" s="18">
         <v>1618</v>
       </c>
@@ -10494,12 +10500,12 @@
       </c>
     </row>
     <row r="78" spans="1:29" ht="16.5">
-      <c r="A78" s="94"/>
-      <c r="B78" s="110" t="s">
+      <c r="A78" s="100"/>
+      <c r="B78" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="C78" s="111"/>
-      <c r="D78" s="112"/>
+      <c r="C78" s="129"/>
+      <c r="D78" s="130"/>
       <c r="E78" s="21" t="s">
         <v>117</v>
       </c>
@@ -10601,12 +10607,12 @@
       </c>
     </row>
     <row r="79" spans="1:29" ht="16.5">
-      <c r="A79" s="94"/>
-      <c r="B79" s="110" t="s">
+      <c r="A79" s="100"/>
+      <c r="B79" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="C79" s="111"/>
-      <c r="D79" s="112"/>
+      <c r="C79" s="129"/>
+      <c r="D79" s="130"/>
       <c r="E79" s="21" t="s">
         <v>118</v>
       </c>
@@ -10708,12 +10714,12 @@
       </c>
     </row>
     <row r="80" spans="1:29" ht="16.5">
-      <c r="A80" s="94"/>
-      <c r="B80" s="110" t="s">
+      <c r="A80" s="100"/>
+      <c r="B80" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="C80" s="111"/>
-      <c r="D80" s="112"/>
+      <c r="C80" s="129"/>
+      <c r="D80" s="130"/>
       <c r="E80" s="21" t="s">
         <v>119</v>
       </c>
@@ -10815,12 +10821,12 @@
       </c>
     </row>
     <row r="81" spans="1:29" ht="16.5">
-      <c r="A81" s="94"/>
-      <c r="B81" s="110" t="s">
+      <c r="A81" s="100"/>
+      <c r="B81" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="C81" s="111"/>
-      <c r="D81" s="112"/>
+      <c r="C81" s="129"/>
+      <c r="D81" s="130"/>
       <c r="E81" s="21" t="s">
         <v>120</v>
       </c>
@@ -10922,14 +10928,14 @@
       </c>
     </row>
     <row r="82" spans="1:29" s="54" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A82" s="155" t="s">
+      <c r="A82" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="B82" s="150" t="s">
+      <c r="B82" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="C82" s="113"/>
-      <c r="D82" s="113"/>
+      <c r="C82" s="146"/>
+      <c r="D82" s="146"/>
       <c r="E82" s="53" t="str">
         <f>+A7</f>
         <v>Nhiệt độ 
@@ -11033,10 +11039,10 @@
       </c>
     </row>
     <row r="83" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A83" s="156"/>
-      <c r="B83" s="151"/>
-      <c r="C83" s="113"/>
-      <c r="D83" s="113"/>
+      <c r="A83" s="82"/>
+      <c r="B83" s="87"/>
+      <c r="C83" s="146"/>
+      <c r="D83" s="146"/>
       <c r="E83" s="53" t="s">
         <v>123</v>
       </c>
@@ -11138,10 +11144,10 @@
       </c>
     </row>
     <row r="84" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A84" s="156"/>
-      <c r="B84" s="151"/>
-      <c r="C84" s="113"/>
-      <c r="D84" s="113"/>
+      <c r="A84" s="82"/>
+      <c r="B84" s="87"/>
+      <c r="C84" s="146"/>
+      <c r="D84" s="146"/>
       <c r="E84" s="53" t="s">
         <v>124</v>
       </c>
@@ -11243,10 +11249,10 @@
       </c>
     </row>
     <row r="85" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A85" s="156"/>
-      <c r="B85" s="151"/>
-      <c r="C85" s="114"/>
-      <c r="D85" s="115"/>
+      <c r="A85" s="82"/>
+      <c r="B85" s="87"/>
+      <c r="C85" s="89"/>
+      <c r="D85" s="90"/>
       <c r="E85" s="53" t="s">
         <v>125</v>
       </c>
@@ -11348,8 +11354,8 @@
       </c>
     </row>
     <row r="86" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A86" s="156"/>
-      <c r="B86" s="151"/>
+      <c r="A86" s="82"/>
+      <c r="B86" s="87"/>
       <c r="C86" s="55"/>
       <c r="D86" s="56"/>
       <c r="E86" s="53" t="s">
@@ -11453,8 +11459,8 @@
       </c>
     </row>
     <row r="87" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A87" s="156"/>
-      <c r="B87" s="151"/>
+      <c r="A87" s="82"/>
+      <c r="B87" s="87"/>
       <c r="C87" s="55"/>
       <c r="D87" s="56"/>
       <c r="E87" s="53" t="s">
@@ -11558,8 +11564,8 @@
       </c>
     </row>
     <row r="88" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A88" s="156"/>
-      <c r="B88" s="151"/>
+      <c r="A88" s="82"/>
+      <c r="B88" s="87"/>
       <c r="C88" s="55"/>
       <c r="D88" s="56"/>
       <c r="E88" s="53" t="s">
@@ -11663,10 +11669,10 @@
       </c>
     </row>
     <row r="89" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A89" s="156"/>
-      <c r="B89" s="152"/>
-      <c r="C89" s="114"/>
-      <c r="D89" s="115"/>
+      <c r="A89" s="82"/>
+      <c r="B89" s="88"/>
+      <c r="C89" s="89"/>
+      <c r="D89" s="90"/>
       <c r="E89" s="53" t="s">
         <v>129</v>
       </c>
@@ -11768,8 +11774,8 @@
       </c>
     </row>
     <row r="90" spans="1:29" s="54" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A90" s="156"/>
-      <c r="B90" s="150" t="s">
+      <c r="A90" s="82"/>
+      <c r="B90" s="86" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="55"/>
@@ -11875,10 +11881,10 @@
       </c>
     </row>
     <row r="91" spans="1:29" s="54" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A91" s="156"/>
-      <c r="B91" s="151"/>
-      <c r="C91" s="158"/>
-      <c r="D91" s="159"/>
+      <c r="A91" s="82"/>
+      <c r="B91" s="87"/>
+      <c r="C91" s="84"/>
+      <c r="D91" s="85"/>
       <c r="E91" s="53" t="s">
         <v>126</v>
       </c>
@@ -11980,10 +11986,10 @@
       </c>
     </row>
     <row r="92" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A92" s="156"/>
-      <c r="B92" s="151"/>
-      <c r="C92" s="158"/>
-      <c r="D92" s="159"/>
+      <c r="A92" s="82"/>
+      <c r="B92" s="87"/>
+      <c r="C92" s="84"/>
+      <c r="D92" s="85"/>
       <c r="E92" s="53" t="s">
         <v>127</v>
       </c>
@@ -12085,10 +12091,10 @@
       </c>
     </row>
     <row r="93" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A93" s="156"/>
-      <c r="B93" s="151"/>
-      <c r="C93" s="158"/>
-      <c r="D93" s="159"/>
+      <c r="A93" s="82"/>
+      <c r="B93" s="87"/>
+      <c r="C93" s="84"/>
+      <c r="D93" s="85"/>
       <c r="E93" s="53" t="s">
         <v>128</v>
       </c>
@@ -12190,16 +12196,16 @@
       </c>
     </row>
     <row r="94" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A94" s="156"/>
-      <c r="B94" s="152"/>
-      <c r="C94" s="158"/>
-      <c r="D94" s="159"/>
+      <c r="A94" s="82"/>
+      <c r="B94" s="88"/>
+      <c r="C94" s="84"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="53" t="s">
         <v>129</v>
       </c>
       <c r="F94" s="25">
         <f>Sheet2!E93</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="25">
         <f>Sheet2!F93</f>
@@ -12295,12 +12301,12 @@
       </c>
     </row>
     <row r="95" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A95" s="156"/>
-      <c r="B95" s="148" t="s">
+      <c r="A95" s="82"/>
+      <c r="B95" s="97" t="s">
         <v>132</v>
       </c>
-      <c r="C95" s="158"/>
-      <c r="D95" s="159"/>
+      <c r="C95" s="84"/>
+      <c r="D95" s="85"/>
       <c r="E95" s="57">
         <v>1603</v>
       </c>
@@ -12402,10 +12408,10 @@
       </c>
     </row>
     <row r="96" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A96" s="156"/>
-      <c r="B96" s="149"/>
-      <c r="C96" s="158"/>
-      <c r="D96" s="159"/>
+      <c r="A96" s="82"/>
+      <c r="B96" s="98"/>
+      <c r="C96" s="84"/>
+      <c r="D96" s="85"/>
       <c r="E96" s="57">
         <v>1608</v>
       </c>
@@ -12507,10 +12513,10 @@
       </c>
     </row>
     <row r="97" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A97" s="156"/>
-      <c r="B97" s="149"/>
-      <c r="C97" s="158"/>
-      <c r="D97" s="159"/>
+      <c r="A97" s="82"/>
+      <c r="B97" s="98"/>
+      <c r="C97" s="84"/>
+      <c r="D97" s="85"/>
       <c r="E97" s="57">
         <v>1613</v>
       </c>
@@ -12612,10 +12618,10 @@
       </c>
     </row>
     <row r="98" spans="1:29" s="54" customFormat="1" ht="16.5">
-      <c r="A98" s="157"/>
-      <c r="B98" s="149"/>
-      <c r="C98" s="158"/>
-      <c r="D98" s="159"/>
+      <c r="A98" s="83"/>
+      <c r="B98" s="98"/>
+      <c r="C98" s="84"/>
+      <c r="D98" s="85"/>
       <c r="E98" s="58">
         <v>1618</v>
       </c>
@@ -12717,228 +12723,228 @@
       </c>
     </row>
     <row r="99" spans="1:29" ht="16.5">
-      <c r="A99" s="142" t="s">
+      <c r="A99" s="91" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="143"/>
-      <c r="C99" s="143"/>
-      <c r="D99" s="144"/>
+      <c r="B99" s="92"/>
+      <c r="C99" s="92"/>
+      <c r="D99" s="93"/>
       <c r="E99" s="16" t="s">
         <v>71</v>
       </c>
       <c r="F99" s="25">
-        <f>Sheet2!E98</f>
+        <f>Sheet2!E51</f>
         <v>0</v>
       </c>
       <c r="G99" s="25">
-        <f>Sheet2!F98</f>
+        <f>Sheet2!F51</f>
         <v>0</v>
       </c>
       <c r="H99" s="25">
-        <f>Sheet2!G98</f>
+        <f>Sheet2!G51</f>
         <v>0</v>
       </c>
       <c r="I99" s="25">
-        <f>Sheet2!H98</f>
+        <f>Sheet2!H51</f>
         <v>0</v>
       </c>
       <c r="J99" s="25">
-        <f>Sheet2!I98</f>
+        <f>Sheet2!I51</f>
         <v>0</v>
       </c>
       <c r="K99" s="25">
-        <f>Sheet2!J98</f>
+        <f>Sheet2!J51</f>
         <v>0</v>
       </c>
       <c r="L99" s="25">
-        <f>Sheet2!K98</f>
+        <f>Sheet2!K51</f>
         <v>0</v>
       </c>
       <c r="M99" s="25">
-        <f>Sheet2!L98</f>
+        <f>Sheet2!L51</f>
         <v>0</v>
       </c>
       <c r="N99" s="25">
-        <f>Sheet2!M98</f>
+        <f>Sheet2!M51</f>
         <v>0</v>
       </c>
       <c r="O99" s="25">
-        <f>Sheet2!N98</f>
+        <f>Sheet2!N51</f>
         <v>0</v>
       </c>
       <c r="P99" s="25">
-        <f>Sheet2!O98</f>
+        <f>Sheet2!O51</f>
         <v>0</v>
       </c>
       <c r="Q99" s="25">
-        <f>Sheet2!P98</f>
+        <f>Sheet2!P51</f>
         <v>0</v>
       </c>
       <c r="R99" s="25">
-        <f>Sheet2!Q98</f>
+        <f>Sheet2!Q51</f>
         <v>0</v>
       </c>
       <c r="S99" s="25">
-        <f>Sheet2!R98</f>
+        <f>Sheet2!R51</f>
         <v>0</v>
       </c>
       <c r="T99" s="25">
-        <f>Sheet2!S98</f>
+        <f>Sheet2!S51</f>
         <v>0</v>
       </c>
       <c r="U99" s="25">
-        <f>Sheet2!T98</f>
+        <f>Sheet2!T51</f>
         <v>0</v>
       </c>
       <c r="V99" s="25">
-        <f>Sheet2!U98</f>
+        <f>Sheet2!U51</f>
         <v>0</v>
       </c>
       <c r="W99" s="25">
-        <f>Sheet2!V98</f>
+        <f>Sheet2!V51</f>
         <v>0</v>
       </c>
       <c r="X99" s="25">
-        <f>Sheet2!W98</f>
+        <f>Sheet2!W51</f>
         <v>0</v>
       </c>
       <c r="Y99" s="25">
-        <f>Sheet2!X98</f>
+        <f>Sheet2!X51</f>
         <v>0</v>
       </c>
       <c r="Z99" s="25">
-        <f>Sheet2!Y98</f>
+        <f>Sheet2!Y51</f>
         <v>0</v>
       </c>
       <c r="AA99" s="25">
-        <f>Sheet2!Z98</f>
+        <f>Sheet2!Z51</f>
         <v>0</v>
       </c>
       <c r="AB99" s="25">
-        <f>Sheet2!AA98</f>
+        <f>Sheet2!AA51</f>
         <v>0</v>
       </c>
       <c r="AC99" s="25">
-        <f>Sheet2!AB98</f>
+        <f>Sheet2!AB51</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:29" ht="16.5" customHeight="1">
-      <c r="A100" s="145" t="s">
+      <c r="A100" s="94" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="146"/>
-      <c r="C100" s="146"/>
-      <c r="D100" s="147"/>
+      <c r="B100" s="95"/>
+      <c r="C100" s="95"/>
+      <c r="D100" s="96"/>
       <c r="E100" s="16"/>
       <c r="F100" s="25">
-        <f>Sheet2!E99</f>
+        <f>Sheet2!E40</f>
         <v>0</v>
       </c>
       <c r="G100" s="25">
-        <f>Sheet2!F99</f>
+        <f>Sheet2!F40</f>
         <v>0</v>
       </c>
       <c r="H100" s="25">
-        <f>Sheet2!G99</f>
+        <f>Sheet2!G40</f>
         <v>0</v>
       </c>
       <c r="I100" s="25">
-        <f>Sheet2!H99</f>
+        <f>Sheet2!H40</f>
         <v>0</v>
       </c>
       <c r="J100" s="25">
-        <f>Sheet2!I99</f>
+        <f>Sheet2!I40</f>
         <v>0</v>
       </c>
       <c r="K100" s="25">
-        <f>Sheet2!J99</f>
+        <f>Sheet2!J40</f>
         <v>0</v>
       </c>
       <c r="L100" s="25">
-        <f>Sheet2!K99</f>
+        <f>Sheet2!K40</f>
         <v>0</v>
       </c>
       <c r="M100" s="25">
-        <f>Sheet2!L99</f>
+        <f>Sheet2!L40</f>
         <v>0</v>
       </c>
       <c r="N100" s="25">
-        <f>Sheet2!M99</f>
+        <f>Sheet2!M40</f>
         <v>0</v>
       </c>
       <c r="O100" s="25">
-        <f>Sheet2!N99</f>
+        <f>Sheet2!N40</f>
         <v>0</v>
       </c>
       <c r="P100" s="25">
-        <f>Sheet2!O99</f>
+        <f>Sheet2!O40</f>
         <v>0</v>
       </c>
       <c r="Q100" s="25">
-        <f>Sheet2!P99</f>
+        <f>Sheet2!P40</f>
         <v>0</v>
       </c>
       <c r="R100" s="25">
-        <f>Sheet2!Q99</f>
+        <f>Sheet2!Q40</f>
         <v>0</v>
       </c>
       <c r="S100" s="25">
-        <f>Sheet2!R99</f>
+        <f>Sheet2!R40</f>
         <v>0</v>
       </c>
       <c r="T100" s="25">
-        <f>Sheet2!S99</f>
+        <f>Sheet2!S40</f>
         <v>0</v>
       </c>
       <c r="U100" s="25">
-        <f>Sheet2!T99</f>
+        <f>Sheet2!T40</f>
         <v>0</v>
       </c>
       <c r="V100" s="25">
-        <f>Sheet2!U99</f>
+        <f>Sheet2!U40</f>
         <v>0</v>
       </c>
       <c r="W100" s="25">
-        <f>Sheet2!V99</f>
+        <f>Sheet2!V40</f>
         <v>0</v>
       </c>
       <c r="X100" s="25">
-        <f>Sheet2!W99</f>
+        <f>Sheet2!W40</f>
         <v>0</v>
       </c>
       <c r="Y100" s="25">
-        <f>Sheet2!X99</f>
+        <f>Sheet2!X40</f>
         <v>0</v>
       </c>
       <c r="Z100" s="25">
-        <f>Sheet2!Y99</f>
+        <f>Sheet2!Y40</f>
         <v>0</v>
       </c>
       <c r="AA100" s="25">
-        <f>Sheet2!Z99</f>
+        <f>Sheet2!Z40</f>
         <v>0</v>
       </c>
       <c r="AB100" s="25">
-        <f>Sheet2!AA99</f>
+        <f>Sheet2!AA40</f>
         <v>0</v>
       </c>
       <c r="AC100" s="25">
-        <f>Sheet2!AB99</f>
+        <f>Sheet2!AB40</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:29" s="54" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A101" s="82" t="s">
+      <c r="A101" s="147" t="s">
         <v>135</v>
       </c>
-      <c r="B101" s="83"/>
-      <c r="C101" s="83"/>
-      <c r="D101" s="84"/>
+      <c r="B101" s="148"/>
+      <c r="C101" s="148"/>
+      <c r="D101" s="149"/>
       <c r="E101" s="58"/>
       <c r="F101" s="25">
         <f>Sheet2!E100</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="25">
         <f>Sheet2!F100</f>
@@ -13034,162 +13040,206 @@
       </c>
     </row>
     <row r="102" spans="1:29" ht="16.5">
-      <c r="A102" s="98" t="s">
+      <c r="A102" s="134" t="s">
         <v>136</v>
       </c>
-      <c r="B102" s="99"/>
-      <c r="C102" s="100"/>
+      <c r="B102" s="135"/>
+      <c r="C102" s="136"/>
       <c r="D102" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E102" s="12"/>
-      <c r="F102" s="107" t="s">
+      <c r="F102" s="143" t="s">
         <v>138</v>
       </c>
-      <c r="G102" s="108"/>
-      <c r="H102" s="108"/>
-      <c r="I102" s="108"/>
-      <c r="J102" s="108"/>
-      <c r="K102" s="108"/>
-      <c r="L102" s="109"/>
-      <c r="M102" s="88" t="s">
+      <c r="G102" s="144"/>
+      <c r="H102" s="144"/>
+      <c r="I102" s="144"/>
+      <c r="J102" s="144"/>
+      <c r="K102" s="144"/>
+      <c r="L102" s="145"/>
+      <c r="M102" s="153" t="s">
         <v>139</v>
       </c>
-      <c r="N102" s="89"/>
-      <c r="O102" s="90"/>
+      <c r="N102" s="154"/>
+      <c r="O102" s="155"/>
       <c r="P102" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="Q102" s="85"/>
-      <c r="R102" s="86"/>
-      <c r="S102" s="86"/>
-      <c r="T102" s="86"/>
-      <c r="U102" s="86"/>
-      <c r="V102" s="86"/>
-      <c r="W102" s="86"/>
-      <c r="X102" s="86"/>
-      <c r="Y102" s="86"/>
-      <c r="Z102" s="86"/>
-      <c r="AA102" s="86"/>
-      <c r="AB102" s="86"/>
-      <c r="AC102" s="86"/>
+      <c r="Q102" s="150"/>
+      <c r="R102" s="151"/>
+      <c r="S102" s="151"/>
+      <c r="T102" s="151"/>
+      <c r="U102" s="151"/>
+      <c r="V102" s="151"/>
+      <c r="W102" s="151"/>
+      <c r="X102" s="151"/>
+      <c r="Y102" s="151"/>
+      <c r="Z102" s="151"/>
+      <c r="AA102" s="151"/>
+      <c r="AB102" s="151"/>
+      <c r="AC102" s="151"/>
     </row>
     <row r="103" spans="1:29" ht="16.5">
-      <c r="A103" s="101"/>
-      <c r="B103" s="102"/>
-      <c r="C103" s="103"/>
+      <c r="A103" s="137"/>
+      <c r="B103" s="138"/>
+      <c r="C103" s="139"/>
       <c r="D103" s="12" t="s">
         <v>141</v>
       </c>
       <c r="E103" s="12"/>
-      <c r="F103" s="95" t="s">
+      <c r="F103" s="131" t="s">
         <v>142</v>
       </c>
-      <c r="G103" s="96"/>
-      <c r="H103" s="96"/>
-      <c r="I103" s="96"/>
-      <c r="J103" s="96"/>
-      <c r="K103" s="96"/>
-      <c r="L103" s="97"/>
-      <c r="M103" s="88"/>
-      <c r="N103" s="89"/>
-      <c r="O103" s="90"/>
+      <c r="G103" s="132"/>
+      <c r="H103" s="132"/>
+      <c r="I103" s="132"/>
+      <c r="J103" s="132"/>
+      <c r="K103" s="132"/>
+      <c r="L103" s="133"/>
+      <c r="M103" s="153"/>
+      <c r="N103" s="154"/>
+      <c r="O103" s="155"/>
       <c r="P103" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="Q103" s="87"/>
-      <c r="R103" s="87"/>
-      <c r="S103" s="87"/>
-      <c r="T103" s="87"/>
-      <c r="U103" s="87"/>
-      <c r="V103" s="87"/>
-      <c r="W103" s="87"/>
-      <c r="X103" s="87"/>
-      <c r="Y103" s="87"/>
-      <c r="Z103" s="87"/>
-      <c r="AA103" s="87"/>
-      <c r="AB103" s="87"/>
-      <c r="AC103" s="87"/>
+      <c r="Q103" s="152"/>
+      <c r="R103" s="152"/>
+      <c r="S103" s="152"/>
+      <c r="T103" s="152"/>
+      <c r="U103" s="152"/>
+      <c r="V103" s="152"/>
+      <c r="W103" s="152"/>
+      <c r="X103" s="152"/>
+      <c r="Y103" s="152"/>
+      <c r="Z103" s="152"/>
+      <c r="AA103" s="152"/>
+      <c r="AB103" s="152"/>
+      <c r="AC103" s="152"/>
     </row>
     <row r="104" spans="1:29" ht="16.5">
-      <c r="A104" s="101"/>
-      <c r="B104" s="102"/>
-      <c r="C104" s="103"/>
-      <c r="D104" s="95"/>
-      <c r="E104" s="96"/>
-      <c r="F104" s="96"/>
-      <c r="G104" s="96"/>
-      <c r="H104" s="96"/>
-      <c r="I104" s="96"/>
-      <c r="J104" s="96"/>
-      <c r="K104" s="96"/>
-      <c r="L104" s="97"/>
-      <c r="M104" s="88"/>
-      <c r="N104" s="89"/>
-      <c r="O104" s="90"/>
+      <c r="A104" s="137"/>
+      <c r="B104" s="138"/>
+      <c r="C104" s="139"/>
+      <c r="D104" s="131"/>
+      <c r="E104" s="132"/>
+      <c r="F104" s="132"/>
+      <c r="G104" s="132"/>
+      <c r="H104" s="132"/>
+      <c r="I104" s="132"/>
+      <c r="J104" s="132"/>
+      <c r="K104" s="132"/>
+      <c r="L104" s="133"/>
+      <c r="M104" s="153"/>
+      <c r="N104" s="154"/>
+      <c r="O104" s="155"/>
       <c r="P104" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="Q104" s="87"/>
-      <c r="R104" s="87"/>
-      <c r="S104" s="87"/>
-      <c r="T104" s="87"/>
-      <c r="U104" s="87"/>
-      <c r="V104" s="87"/>
-      <c r="W104" s="87"/>
-      <c r="X104" s="87"/>
-      <c r="Y104" s="87"/>
-      <c r="Z104" s="87"/>
-      <c r="AA104" s="87"/>
-      <c r="AB104" s="87"/>
-      <c r="AC104" s="87"/>
+      <c r="Q104" s="152"/>
+      <c r="R104" s="152"/>
+      <c r="S104" s="152"/>
+      <c r="T104" s="152"/>
+      <c r="U104" s="152"/>
+      <c r="V104" s="152"/>
+      <c r="W104" s="152"/>
+      <c r="X104" s="152"/>
+      <c r="Y104" s="152"/>
+      <c r="Z104" s="152"/>
+      <c r="AA104" s="152"/>
+      <c r="AB104" s="152"/>
+      <c r="AC104" s="152"/>
     </row>
     <row r="105" spans="1:29" ht="16.5">
-      <c r="A105" s="104"/>
-      <c r="B105" s="105"/>
-      <c r="C105" s="106"/>
-      <c r="D105" s="95"/>
-      <c r="E105" s="96"/>
-      <c r="F105" s="96"/>
-      <c r="G105" s="96"/>
-      <c r="H105" s="96"/>
-      <c r="I105" s="96"/>
-      <c r="J105" s="96"/>
-      <c r="K105" s="96"/>
-      <c r="L105" s="97"/>
-      <c r="M105" s="91"/>
-      <c r="N105" s="92"/>
-      <c r="O105" s="93"/>
+      <c r="A105" s="140"/>
+      <c r="B105" s="141"/>
+      <c r="C105" s="142"/>
+      <c r="D105" s="131"/>
+      <c r="E105" s="132"/>
+      <c r="F105" s="132"/>
+      <c r="G105" s="132"/>
+      <c r="H105" s="132"/>
+      <c r="I105" s="132"/>
+      <c r="J105" s="132"/>
+      <c r="K105" s="132"/>
+      <c r="L105" s="133"/>
+      <c r="M105" s="156"/>
+      <c r="N105" s="157"/>
+      <c r="O105" s="158"/>
       <c r="P105" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="Q105" s="87"/>
-      <c r="R105" s="87"/>
-      <c r="S105" s="87"/>
-      <c r="T105" s="87"/>
-      <c r="U105" s="87"/>
-      <c r="V105" s="87"/>
-      <c r="W105" s="87"/>
-      <c r="X105" s="87"/>
-      <c r="Y105" s="87"/>
-      <c r="Z105" s="87"/>
-      <c r="AA105" s="87"/>
-      <c r="AB105" s="87"/>
-      <c r="AC105" s="87"/>
+      <c r="Q105" s="152"/>
+      <c r="R105" s="152"/>
+      <c r="S105" s="152"/>
+      <c r="T105" s="152"/>
+      <c r="U105" s="152"/>
+      <c r="V105" s="152"/>
+      <c r="W105" s="152"/>
+      <c r="X105" s="152"/>
+      <c r="Y105" s="152"/>
+      <c r="Z105" s="152"/>
+      <c r="AA105" s="152"/>
+      <c r="AB105" s="152"/>
+      <c r="AC105" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="A82:A98"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="B90:B94"/>
-    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="Q102:AC102"/>
+    <mergeCell ref="Q103:AC103"/>
+    <mergeCell ref="Q104:AC104"/>
+    <mergeCell ref="Q105:AC105"/>
+    <mergeCell ref="M102:O105"/>
+    <mergeCell ref="A41:A59"/>
+    <mergeCell ref="A60:A81"/>
+    <mergeCell ref="D105:L105"/>
+    <mergeCell ref="A102:C105"/>
+    <mergeCell ref="F102:L102"/>
+    <mergeCell ref="F103:L103"/>
+    <mergeCell ref="D104:L104"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:C73"/>
+    <mergeCell ref="B74:C77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="G3:V3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="G5:V5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B28:D29"/>
+    <mergeCell ref="B20:D27"/>
+    <mergeCell ref="B14:D19"/>
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A100:D100"/>
     <mergeCell ref="B95:B98"/>
@@ -13206,61 +13256,17 @@
     <mergeCell ref="B39:C40"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G3:V3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="G5:V5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="B20:D27"/>
-    <mergeCell ref="B14:D19"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="A41:A59"/>
-    <mergeCell ref="A60:A81"/>
-    <mergeCell ref="D105:L105"/>
-    <mergeCell ref="A102:C105"/>
-    <mergeCell ref="F102:L102"/>
-    <mergeCell ref="F103:L103"/>
-    <mergeCell ref="D104:L104"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:C73"/>
-    <mergeCell ref="B74:C77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="Q102:AC102"/>
-    <mergeCell ref="Q103:AC103"/>
-    <mergeCell ref="Q104:AC104"/>
-    <mergeCell ref="Q105:AC105"/>
-    <mergeCell ref="M102:O105"/>
+    <mergeCell ref="A82:A98"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="B90:B94"/>
+    <mergeCell ref="C85:D85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13279,9 +13285,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" s="160"/>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
+      <c r="A1" s="176"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
       <c r="D1" s="67"/>
       <c r="E1" s="67"/>
       <c r="F1" s="67"/>
@@ -13295,56 +13301,56 @@
       <c r="N1" s="67"/>
       <c r="O1" s="67"/>
       <c r="P1" s="67"/>
-      <c r="Q1" s="161" t="s">
+      <c r="Q1" s="177" t="s">
         <v>161</v>
       </c>
-      <c r="R1" s="161"/>
-      <c r="S1" s="161"/>
-      <c r="T1" s="161"/>
+      <c r="R1" s="177"/>
+      <c r="S1" s="177"/>
+      <c r="T1" s="177"/>
     </row>
     <row r="2" spans="1:28">
-      <c r="A2" s="160"/>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="162" t="s">
+      <c r="A2" s="176"/>
+      <c r="B2" s="176"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="163" t="s">
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="178"/>
+      <c r="M2" s="178"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="178"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="179" t="s">
         <v>162</v>
       </c>
-      <c r="R2" s="163"/>
-      <c r="S2" s="163"/>
-      <c r="T2" s="163"/>
+      <c r="R2" s="179"/>
+      <c r="S2" s="179"/>
+      <c r="T2" s="179"/>
     </row>
     <row r="3" spans="1:28">
-      <c r="A3" s="160"/>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="162"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
+      <c r="A3" s="176"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="178"/>
+      <c r="O3" s="178"/>
+      <c r="P3" s="178"/>
       <c r="Q3" s="67"/>
       <c r="R3" s="67"/>
       <c r="S3" s="67"/>
@@ -13457,16 +13463,16 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="15">
-      <c r="A6" s="164" t="s">
+      <c r="A6" s="166" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="167" t="s">
+      <c r="B6" s="169" t="s">
         <v>167</v>
       </c>
       <c r="C6" s="76">
         <v>5404</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="72" t="s">
         <v>175</v>
       </c>
       <c r="E6" s="80"/>
@@ -13495,12 +13501,12 @@
       <c r="AB6" s="80"/>
     </row>
     <row r="7" spans="1:28" ht="15">
-      <c r="A7" s="165"/>
-      <c r="B7" s="168"/>
+      <c r="A7" s="167"/>
+      <c r="B7" s="170"/>
       <c r="C7" s="76">
         <v>5408</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="72" t="s">
         <v>176</v>
       </c>
       <c r="E7" s="80"/>
@@ -13529,12 +13535,12 @@
       <c r="AB7" s="80"/>
     </row>
     <row r="8" spans="1:28" ht="15">
-      <c r="A8" s="165"/>
-      <c r="B8" s="168"/>
+      <c r="A8" s="167"/>
+      <c r="B8" s="170"/>
       <c r="C8" s="76">
         <v>5414</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E8" s="80"/>
@@ -13563,12 +13569,12 @@
       <c r="AB8" s="80"/>
     </row>
     <row r="9" spans="1:28" ht="15">
-      <c r="A9" s="165"/>
-      <c r="B9" s="169"/>
+      <c r="A9" s="167"/>
+      <c r="B9" s="171"/>
       <c r="C9" s="76">
         <v>5418</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="72" t="s">
         <v>178</v>
       </c>
       <c r="E9" s="80"/>
@@ -13597,14 +13603,14 @@
       <c r="AB9" s="80"/>
     </row>
     <row r="10" spans="1:28" ht="15">
-      <c r="A10" s="165"/>
-      <c r="B10" s="167" t="s">
+      <c r="A10" s="167"/>
+      <c r="B10" s="169" t="s">
         <v>168</v>
       </c>
       <c r="C10" s="76">
         <v>4405</v>
       </c>
-      <c r="D10" s="81" t="s">
+      <c r="D10" s="72" t="s">
         <v>179</v>
       </c>
       <c r="E10" s="80"/>
@@ -13633,12 +13639,12 @@
       <c r="AB10" s="80"/>
     </row>
     <row r="11" spans="1:28" ht="15">
-      <c r="A11" s="165"/>
-      <c r="B11" s="168"/>
+      <c r="A11" s="167"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="76">
         <v>4412</v>
       </c>
-      <c r="D11" s="81" t="s">
+      <c r="D11" s="72" t="s">
         <v>180</v>
       </c>
       <c r="E11" s="80"/>
@@ -13667,12 +13673,12 @@
       <c r="AB11" s="80"/>
     </row>
     <row r="12" spans="1:28" ht="15">
-      <c r="A12" s="165"/>
-      <c r="B12" s="169"/>
+      <c r="A12" s="167"/>
+      <c r="B12" s="171"/>
       <c r="C12" s="76">
         <v>4420</v>
       </c>
-      <c r="D12" s="81" t="s">
+      <c r="D12" s="72" t="s">
         <v>181</v>
       </c>
       <c r="E12" s="80"/>
@@ -13701,14 +13707,14 @@
       <c r="AB12" s="80"/>
     </row>
     <row r="13" spans="1:28" ht="15">
-      <c r="A13" s="165"/>
-      <c r="B13" s="164" t="s">
+      <c r="A13" s="167"/>
+      <c r="B13" s="166" t="s">
         <v>169</v>
       </c>
       <c r="C13" s="72">
         <v>4402</v>
       </c>
-      <c r="D13" s="81" t="s">
+      <c r="D13" s="72" t="s">
         <v>182</v>
       </c>
       <c r="E13" s="80"/>
@@ -13737,12 +13743,12 @@
       <c r="AB13" s="80"/>
     </row>
     <row r="14" spans="1:28" ht="15">
-      <c r="A14" s="165"/>
-      <c r="B14" s="165"/>
+      <c r="A14" s="167"/>
+      <c r="B14" s="167"/>
       <c r="C14" s="72">
         <v>4405</v>
       </c>
-      <c r="D14" s="81" t="s">
+      <c r="D14" s="72" t="s">
         <v>183</v>
       </c>
       <c r="E14" s="80"/>
@@ -13771,12 +13777,12 @@
       <c r="AB14" s="80"/>
     </row>
     <row r="15" spans="1:28" ht="15">
-      <c r="A15" s="165"/>
-      <c r="B15" s="165"/>
+      <c r="A15" s="167"/>
+      <c r="B15" s="167"/>
       <c r="C15" s="72">
         <v>4409</v>
       </c>
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="72" t="s">
         <v>184</v>
       </c>
       <c r="E15" s="80"/>
@@ -13805,12 +13811,12 @@
       <c r="AB15" s="80"/>
     </row>
     <row r="16" spans="1:28" ht="15">
-      <c r="A16" s="165"/>
-      <c r="B16" s="165"/>
+      <c r="A16" s="167"/>
+      <c r="B16" s="167"/>
       <c r="C16" s="72">
         <v>4412</v>
       </c>
-      <c r="D16" s="81" t="s">
+      <c r="D16" s="72" t="s">
         <v>185</v>
       </c>
       <c r="E16" s="80"/>
@@ -13839,12 +13845,12 @@
       <c r="AB16" s="80"/>
     </row>
     <row r="17" spans="1:28" ht="15">
-      <c r="A17" s="165"/>
-      <c r="B17" s="165"/>
+      <c r="A17" s="167"/>
+      <c r="B17" s="167"/>
       <c r="C17" s="72">
         <v>4415</v>
       </c>
-      <c r="D17" s="81" t="s">
+      <c r="D17" s="72" t="s">
         <v>186</v>
       </c>
       <c r="E17" s="80"/>
@@ -13873,12 +13879,12 @@
       <c r="AB17" s="80"/>
     </row>
     <row r="18" spans="1:28" ht="15">
-      <c r="A18" s="165"/>
-      <c r="B18" s="166"/>
+      <c r="A18" s="167"/>
+      <c r="B18" s="168"/>
       <c r="C18" s="72">
         <v>4419</v>
       </c>
-      <c r="D18" s="81" t="s">
+      <c r="D18" s="72" t="s">
         <v>187</v>
       </c>
       <c r="E18" s="80"/>
@@ -13907,14 +13913,14 @@
       <c r="AB18" s="80"/>
     </row>
     <row r="19" spans="1:28" ht="15">
-      <c r="A19" s="165"/>
-      <c r="B19" s="164" t="s">
+      <c r="A19" s="167"/>
+      <c r="B19" s="166" t="s">
         <v>170</v>
       </c>
       <c r="C19" s="72">
         <v>3201</v>
       </c>
-      <c r="D19" s="81" t="s">
+      <c r="D19" s="72" t="s">
         <v>188</v>
       </c>
       <c r="E19" s="80"/>
@@ -13943,12 +13949,12 @@
       <c r="AB19" s="80"/>
     </row>
     <row r="20" spans="1:28" ht="15">
-      <c r="A20" s="165"/>
-      <c r="B20" s="165"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="167"/>
       <c r="C20" s="72">
         <v>3203</v>
       </c>
-      <c r="D20" s="81" t="s">
+      <c r="D20" s="72" t="s">
         <v>189</v>
       </c>
       <c r="E20" s="80"/>
@@ -13977,12 +13983,12 @@
       <c r="AB20" s="80"/>
     </row>
     <row r="21" spans="1:28" ht="15">
-      <c r="A21" s="165"/>
-      <c r="B21" s="165"/>
+      <c r="A21" s="167"/>
+      <c r="B21" s="167"/>
       <c r="C21" s="72">
         <v>3206</v>
       </c>
-      <c r="D21" s="81" t="s">
+      <c r="D21" s="72" t="s">
         <v>190</v>
       </c>
       <c r="E21" s="80"/>
@@ -14011,12 +14017,12 @@
       <c r="AB21" s="80"/>
     </row>
     <row r="22" spans="1:28" ht="15">
-      <c r="A22" s="165"/>
-      <c r="B22" s="165"/>
+      <c r="A22" s="167"/>
+      <c r="B22" s="167"/>
       <c r="C22" s="72">
         <v>3208</v>
       </c>
-      <c r="D22" s="81" t="s">
+      <c r="D22" s="72" t="s">
         <v>191</v>
       </c>
       <c r="E22" s="80"/>
@@ -14045,12 +14051,12 @@
       <c r="AB22" s="80"/>
     </row>
     <row r="23" spans="1:28" ht="15">
-      <c r="A23" s="165"/>
-      <c r="B23" s="165"/>
+      <c r="A23" s="167"/>
+      <c r="B23" s="167"/>
       <c r="C23" s="72">
         <v>3211</v>
       </c>
-      <c r="D23" s="81" t="s">
+      <c r="D23" s="72" t="s">
         <v>192</v>
       </c>
       <c r="E23" s="80"/>
@@ -14079,12 +14085,12 @@
       <c r="AB23" s="80"/>
     </row>
     <row r="24" spans="1:28" ht="15">
-      <c r="A24" s="165"/>
-      <c r="B24" s="165"/>
+      <c r="A24" s="167"/>
+      <c r="B24" s="167"/>
       <c r="C24" s="72">
         <v>3213</v>
       </c>
-      <c r="D24" s="81" t="s">
+      <c r="D24" s="72" t="s">
         <v>193</v>
       </c>
       <c r="E24" s="80"/>
@@ -14113,12 +14119,12 @@
       <c r="AB24" s="80"/>
     </row>
     <row r="25" spans="1:28" ht="15">
-      <c r="A25" s="165"/>
-      <c r="B25" s="165"/>
+      <c r="A25" s="167"/>
+      <c r="B25" s="167"/>
       <c r="C25" s="72">
         <v>3216</v>
       </c>
-      <c r="D25" s="81" t="s">
+      <c r="D25" s="72" t="s">
         <v>194</v>
       </c>
       <c r="E25" s="80"/>
@@ -14147,12 +14153,12 @@
       <c r="AB25" s="80"/>
     </row>
     <row r="26" spans="1:28" ht="15">
-      <c r="A26" s="165"/>
-      <c r="B26" s="166"/>
+      <c r="A26" s="167"/>
+      <c r="B26" s="168"/>
       <c r="C26" s="72">
         <v>3218</v>
       </c>
-      <c r="D26" s="81" t="s">
+      <c r="D26" s="72" t="s">
         <v>195</v>
       </c>
       <c r="E26" s="80"/>
@@ -14181,14 +14187,14 @@
       <c r="AB26" s="80"/>
     </row>
     <row r="27" spans="1:28" ht="15">
-      <c r="A27" s="165"/>
-      <c r="B27" s="164" t="s">
+      <c r="A27" s="167"/>
+      <c r="B27" s="166" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="72">
         <v>1808</v>
       </c>
-      <c r="D27" s="81" t="s">
+      <c r="D27" s="72" t="s">
         <v>196</v>
       </c>
       <c r="E27" s="80"/>
@@ -14217,12 +14223,12 @@
       <c r="AB27" s="80"/>
     </row>
     <row r="28" spans="1:28" ht="15">
-      <c r="A28" s="165"/>
-      <c r="B28" s="166"/>
+      <c r="A28" s="167"/>
+      <c r="B28" s="168"/>
       <c r="C28" s="77">
         <v>1818</v>
       </c>
-      <c r="D28" s="81" t="s">
+      <c r="D28" s="72" t="s">
         <v>197</v>
       </c>
       <c r="E28" s="80"/>
@@ -14251,14 +14257,14 @@
       <c r="AB28" s="80"/>
     </row>
     <row r="29" spans="1:28" ht="15">
-      <c r="A29" s="165"/>
-      <c r="B29" s="164" t="s">
+      <c r="A29" s="167"/>
+      <c r="B29" s="166" t="s">
         <v>35</v>
       </c>
       <c r="C29" s="77">
         <v>1403</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="72" t="s">
         <v>198</v>
       </c>
       <c r="E29" s="80"/>
@@ -14287,12 +14293,12 @@
       <c r="AB29" s="80"/>
     </row>
     <row r="30" spans="1:28" ht="15">
-      <c r="A30" s="165"/>
-      <c r="B30" s="165"/>
+      <c r="A30" s="167"/>
+      <c r="B30" s="167"/>
       <c r="C30" s="78">
         <v>1408</v>
       </c>
-      <c r="D30" s="81" t="s">
+      <c r="D30" s="72" t="s">
         <v>199</v>
       </c>
       <c r="E30" s="80"/>
@@ -14321,12 +14327,12 @@
       <c r="AB30" s="80"/>
     </row>
     <row r="31" spans="1:28" ht="15">
-      <c r="A31" s="165"/>
-      <c r="B31" s="165"/>
+      <c r="A31" s="167"/>
+      <c r="B31" s="167"/>
       <c r="C31" s="78">
         <v>1413</v>
       </c>
-      <c r="D31" s="81" t="s">
+      <c r="D31" s="72" t="s">
         <v>200</v>
       </c>
       <c r="E31" s="80"/>
@@ -14355,12 +14361,12 @@
       <c r="AB31" s="80"/>
     </row>
     <row r="32" spans="1:28" ht="15">
-      <c r="A32" s="165"/>
-      <c r="B32" s="166"/>
+      <c r="A32" s="167"/>
+      <c r="B32" s="168"/>
       <c r="C32" s="78">
         <v>1418</v>
       </c>
-      <c r="D32" s="81" t="s">
+      <c r="D32" s="72" t="s">
         <v>201</v>
       </c>
       <c r="E32" s="80"/>
@@ -14389,14 +14395,14 @@
       <c r="AB32" s="80"/>
     </row>
     <row r="33" spans="1:28" ht="15">
-      <c r="A33" s="165"/>
+      <c r="A33" s="167"/>
       <c r="B33" s="78" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="72">
         <v>4311</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="72" t="s">
         <v>202</v>
       </c>
       <c r="E33" s="80"/>
@@ -14425,14 +14431,14 @@
       <c r="AB33" s="80"/>
     </row>
     <row r="34" spans="1:28" ht="30">
-      <c r="A34" s="165"/>
-      <c r="B34" s="164" t="s">
+      <c r="A34" s="167"/>
+      <c r="B34" s="166" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="81" t="s">
+      <c r="D34" s="72" t="s">
         <v>203</v>
       </c>
       <c r="E34" s="80"/>
@@ -14461,12 +14467,12 @@
       <c r="AB34" s="80"/>
     </row>
     <row r="35" spans="1:28" ht="30">
-      <c r="A35" s="165"/>
-      <c r="B35" s="165"/>
+      <c r="A35" s="167"/>
+      <c r="B35" s="167"/>
       <c r="C35" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="81" t="s">
+      <c r="D35" s="72" t="s">
         <v>204</v>
       </c>
       <c r="E35" s="80"/>
@@ -14495,12 +14501,12 @@
       <c r="AB35" s="80"/>
     </row>
     <row r="36" spans="1:28" ht="30">
-      <c r="A36" s="165"/>
-      <c r="B36" s="166"/>
+      <c r="A36" s="167"/>
+      <c r="B36" s="168"/>
       <c r="C36" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="81" t="s">
+      <c r="D36" s="72" t="s">
         <v>205</v>
       </c>
       <c r="E36" s="80"/>
@@ -14529,12 +14535,12 @@
       <c r="AB36" s="80"/>
     </row>
     <row r="37" spans="1:28" ht="15">
-      <c r="A37" s="165"/>
-      <c r="B37" s="170" t="s">
+      <c r="A37" s="167"/>
+      <c r="B37" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="171"/>
-      <c r="D37" s="81" t="s">
+      <c r="C37" s="161"/>
+      <c r="D37" s="72" t="s">
         <v>206</v>
       </c>
       <c r="E37" s="80"/>
@@ -14563,14 +14569,14 @@
       <c r="AB37" s="80"/>
     </row>
     <row r="38" spans="1:28" ht="16.5">
-      <c r="A38" s="165"/>
-      <c r="B38" s="164" t="s">
+      <c r="A38" s="167"/>
+      <c r="B38" s="166" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="81" t="s">
+      <c r="D38" s="72" t="s">
         <v>207</v>
       </c>
       <c r="E38" s="80"/>
@@ -14599,12 +14605,12 @@
       <c r="AB38" s="80"/>
     </row>
     <row r="39" spans="1:28" ht="16.5">
-      <c r="A39" s="166"/>
-      <c r="B39" s="166"/>
+      <c r="A39" s="168"/>
+      <c r="B39" s="168"/>
       <c r="C39" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D39" s="81" t="s">
+      <c r="D39" s="72" t="s">
         <v>208</v>
       </c>
       <c r="E39" s="80"/>
@@ -14633,14 +14639,14 @@
       <c r="AB39" s="80"/>
     </row>
     <row r="40" spans="1:28" ht="16.5">
-      <c r="A40" s="164" t="s">
+      <c r="A40" s="166" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="175" t="s">
+      <c r="B40" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="176"/>
-      <c r="D40" s="81" t="s">
+      <c r="C40" s="175"/>
+      <c r="D40" s="72" t="s">
         <v>209</v>
       </c>
       <c r="E40" s="80"/>
@@ -14669,12 +14675,12 @@
       <c r="AB40" s="80"/>
     </row>
     <row r="41" spans="1:28" ht="16.5">
-      <c r="A41" s="165"/>
+      <c r="A41" s="167"/>
       <c r="B41" s="172" t="s">
         <v>50</v>
       </c>
       <c r="C41" s="173"/>
-      <c r="D41" s="81" t="s">
+      <c r="D41" s="72" t="s">
         <v>210</v>
       </c>
       <c r="E41" s="80"/>
@@ -14703,12 +14709,12 @@
       <c r="AB41" s="80"/>
     </row>
     <row r="42" spans="1:28" ht="16.5">
-      <c r="A42" s="165"/>
+      <c r="A42" s="167"/>
       <c r="B42" s="172" t="s">
         <v>52</v>
       </c>
       <c r="C42" s="173"/>
-      <c r="D42" s="81" t="s">
+      <c r="D42" s="72" t="s">
         <v>211</v>
       </c>
       <c r="E42" s="80"/>
@@ -14737,12 +14743,12 @@
       <c r="AB42" s="80"/>
     </row>
     <row r="43" spans="1:28" ht="16.5">
-      <c r="A43" s="165"/>
+      <c r="A43" s="167"/>
       <c r="B43" s="172" t="s">
         <v>54</v>
       </c>
       <c r="C43" s="173"/>
-      <c r="D43" s="81" t="s">
+      <c r="D43" s="72" t="s">
         <v>212</v>
       </c>
       <c r="E43" s="80"/>
@@ -14771,12 +14777,12 @@
       <c r="AB43" s="80"/>
     </row>
     <row r="44" spans="1:28" ht="16.5">
-      <c r="A44" s="165"/>
+      <c r="A44" s="167"/>
       <c r="B44" s="172" t="s">
         <v>56</v>
       </c>
       <c r="C44" s="173"/>
-      <c r="D44" s="81" t="s">
+      <c r="D44" s="72" t="s">
         <v>213</v>
       </c>
       <c r="E44" s="80"/>
@@ -14805,12 +14811,12 @@
       <c r="AB44" s="80"/>
     </row>
     <row r="45" spans="1:28" ht="16.5">
-      <c r="A45" s="165"/>
+      <c r="A45" s="167"/>
       <c r="B45" s="172" t="s">
         <v>58</v>
       </c>
       <c r="C45" s="173"/>
-      <c r="D45" s="81" t="s">
+      <c r="D45" s="72" t="s">
         <v>214</v>
       </c>
       <c r="E45" s="80"/>
@@ -14839,12 +14845,12 @@
       <c r="AB45" s="80"/>
     </row>
     <row r="46" spans="1:28" ht="16.5">
-      <c r="A46" s="165"/>
+      <c r="A46" s="167"/>
       <c r="B46" s="172" t="s">
         <v>60</v>
       </c>
       <c r="C46" s="173"/>
-      <c r="D46" s="81" t="s">
+      <c r="D46" s="72" t="s">
         <v>215</v>
       </c>
       <c r="E46" s="80"/>
@@ -14873,12 +14879,12 @@
       <c r="AB46" s="80"/>
     </row>
     <row r="47" spans="1:28" ht="16.5">
-      <c r="A47" s="165"/>
+      <c r="A47" s="167"/>
       <c r="B47" s="172" t="s">
         <v>62</v>
       </c>
       <c r="C47" s="173"/>
-      <c r="D47" s="81" t="s">
+      <c r="D47" s="72" t="s">
         <v>216</v>
       </c>
       <c r="E47" s="80"/>
@@ -14907,12 +14913,12 @@
       <c r="AB47" s="80"/>
     </row>
     <row r="48" spans="1:28" ht="16.5">
-      <c r="A48" s="165"/>
+      <c r="A48" s="167"/>
       <c r="B48" s="172" t="s">
         <v>64</v>
       </c>
       <c r="C48" s="173"/>
-      <c r="D48" s="81" t="s">
+      <c r="D48" s="72" t="s">
         <v>217</v>
       </c>
       <c r="E48" s="80"/>
@@ -14941,12 +14947,12 @@
       <c r="AB48" s="80"/>
     </row>
     <row r="49" spans="1:28" ht="16.5">
-      <c r="A49" s="165"/>
+      <c r="A49" s="167"/>
       <c r="B49" s="172" t="s">
         <v>66</v>
       </c>
       <c r="C49" s="173"/>
-      <c r="D49" s="81" t="s">
+      <c r="D49" s="72" t="s">
         <v>218</v>
       </c>
       <c r="E49" s="80"/>
@@ -14975,12 +14981,12 @@
       <c r="AB49" s="80"/>
     </row>
     <row r="50" spans="1:28" ht="16.5">
-      <c r="A50" s="165"/>
+      <c r="A50" s="167"/>
       <c r="B50" s="172" t="s">
         <v>68</v>
       </c>
       <c r="C50" s="173"/>
-      <c r="D50" s="81" t="s">
+      <c r="D50" s="72" t="s">
         <v>219</v>
       </c>
       <c r="E50" s="80"/>
@@ -15009,12 +15015,12 @@
       <c r="AB50" s="80"/>
     </row>
     <row r="51" spans="1:28" ht="16.5">
-      <c r="A51" s="165"/>
+      <c r="A51" s="167"/>
       <c r="B51" s="172" t="s">
         <v>70</v>
       </c>
       <c r="C51" s="173"/>
-      <c r="D51" s="81" t="s">
+      <c r="D51" s="72" t="s">
         <v>220</v>
       </c>
       <c r="E51" s="80"/>
@@ -15043,12 +15049,12 @@
       <c r="AB51" s="80"/>
     </row>
     <row r="52" spans="1:28" ht="16.5">
-      <c r="A52" s="165"/>
+      <c r="A52" s="167"/>
       <c r="B52" s="172" t="s">
         <v>72</v>
       </c>
       <c r="C52" s="173"/>
-      <c r="D52" s="81" t="s">
+      <c r="D52" s="72" t="s">
         <v>221</v>
       </c>
       <c r="E52" s="80"/>
@@ -15077,12 +15083,12 @@
       <c r="AB52" s="80"/>
     </row>
     <row r="53" spans="1:28" ht="16.5">
-      <c r="A53" s="165"/>
+      <c r="A53" s="167"/>
       <c r="B53" s="172" t="s">
         <v>74</v>
       </c>
       <c r="C53" s="173"/>
-      <c r="D53" s="81" t="s">
+      <c r="D53" s="72" t="s">
         <v>222</v>
       </c>
       <c r="E53" s="80"/>
@@ -15111,12 +15117,12 @@
       <c r="AB53" s="80"/>
     </row>
     <row r="54" spans="1:28" ht="16.5">
-      <c r="A54" s="165"/>
+      <c r="A54" s="167"/>
       <c r="B54" s="172" t="s">
         <v>76</v>
       </c>
       <c r="C54" s="173"/>
-      <c r="D54" s="81" t="s">
+      <c r="D54" s="72" t="s">
         <v>223</v>
       </c>
       <c r="E54" s="80"/>
@@ -15145,12 +15151,12 @@
       <c r="AB54" s="80"/>
     </row>
     <row r="55" spans="1:28" ht="16.5">
-      <c r="A55" s="165"/>
+      <c r="A55" s="167"/>
       <c r="B55" s="172" t="s">
         <v>78</v>
       </c>
       <c r="C55" s="173"/>
-      <c r="D55" s="81" t="s">
+      <c r="D55" s="72" t="s">
         <v>224</v>
       </c>
       <c r="E55" s="80"/>
@@ -15179,12 +15185,12 @@
       <c r="AB55" s="80"/>
     </row>
     <row r="56" spans="1:28" ht="16.5">
-      <c r="A56" s="165"/>
+      <c r="A56" s="167"/>
       <c r="B56" s="172" t="s">
         <v>80</v>
       </c>
       <c r="C56" s="173"/>
-      <c r="D56" s="81" t="s">
+      <c r="D56" s="72" t="s">
         <v>225</v>
       </c>
       <c r="E56" s="80"/>
@@ -15213,12 +15219,12 @@
       <c r="AB56" s="80"/>
     </row>
     <row r="57" spans="1:28" ht="16.5">
-      <c r="A57" s="165"/>
+      <c r="A57" s="167"/>
       <c r="B57" s="172" t="s">
         <v>82</v>
       </c>
       <c r="C57" s="173"/>
-      <c r="D57" s="81" t="s">
+      <c r="D57" s="72" t="s">
         <v>226</v>
       </c>
       <c r="E57" s="80"/>
@@ -15247,12 +15253,12 @@
       <c r="AB57" s="80"/>
     </row>
     <row r="58" spans="1:28" ht="16.5">
-      <c r="A58" s="166"/>
+      <c r="A58" s="168"/>
       <c r="B58" s="172" t="s">
         <v>84</v>
       </c>
       <c r="C58" s="173"/>
-      <c r="D58" s="81" t="s">
+      <c r="D58" s="72" t="s">
         <v>227</v>
       </c>
       <c r="E58" s="80"/>
@@ -15281,14 +15287,14 @@
       <c r="AB58" s="80"/>
     </row>
     <row r="59" spans="1:28" ht="15">
-      <c r="A59" s="167" t="s">
+      <c r="A59" s="169" t="s">
         <v>171</v>
       </c>
-      <c r="B59" s="174" t="s">
+      <c r="B59" s="165" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="174"/>
-      <c r="D59" s="81" t="s">
+      <c r="C59" s="165"/>
+      <c r="D59" s="72" t="s">
         <v>228</v>
       </c>
       <c r="E59" s="80"/>
@@ -15317,12 +15323,12 @@
       <c r="AB59" s="80"/>
     </row>
     <row r="60" spans="1:28" ht="15">
-      <c r="A60" s="168"/>
-      <c r="B60" s="174" t="s">
+      <c r="A60" s="170"/>
+      <c r="B60" s="165" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="174"/>
-      <c r="D60" s="81" t="s">
+      <c r="C60" s="165"/>
+      <c r="D60" s="72" t="s">
         <v>229</v>
       </c>
       <c r="E60" s="80"/>
@@ -15351,12 +15357,12 @@
       <c r="AB60" s="80"/>
     </row>
     <row r="61" spans="1:28" ht="15">
-      <c r="A61" s="168"/>
-      <c r="B61" s="174" t="s">
+      <c r="A61" s="170"/>
+      <c r="B61" s="165" t="s">
         <v>91</v>
       </c>
-      <c r="C61" s="174"/>
-      <c r="D61" s="81" t="s">
+      <c r="C61" s="165"/>
+      <c r="D61" s="72" t="s">
         <v>230</v>
       </c>
       <c r="E61" s="80"/>
@@ -15385,12 +15391,12 @@
       <c r="AB61" s="80"/>
     </row>
     <row r="62" spans="1:28" ht="15">
-      <c r="A62" s="168"/>
-      <c r="B62" s="174" t="s">
+      <c r="A62" s="170"/>
+      <c r="B62" s="165" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="174"/>
-      <c r="D62" s="81" t="s">
+      <c r="C62" s="165"/>
+      <c r="D62" s="72" t="s">
         <v>231</v>
       </c>
       <c r="E62" s="80"/>
@@ -15419,12 +15425,12 @@
       <c r="AB62" s="80"/>
     </row>
     <row r="63" spans="1:28" ht="15">
-      <c r="A63" s="168"/>
-      <c r="B63" s="174" t="s">
+      <c r="A63" s="170"/>
+      <c r="B63" s="165" t="s">
         <v>95</v>
       </c>
-      <c r="C63" s="174"/>
-      <c r="D63" s="81" t="s">
+      <c r="C63" s="165"/>
+      <c r="D63" s="72" t="s">
         <v>232</v>
       </c>
       <c r="E63" s="80"/>
@@ -15453,12 +15459,12 @@
       <c r="AB63" s="80"/>
     </row>
     <row r="64" spans="1:28" ht="15">
-      <c r="A64" s="168"/>
-      <c r="B64" s="174" t="s">
+      <c r="A64" s="170"/>
+      <c r="B64" s="165" t="s">
         <v>97</v>
       </c>
-      <c r="C64" s="174"/>
-      <c r="D64" s="81" t="s">
+      <c r="C64" s="165"/>
+      <c r="D64" s="72" t="s">
         <v>233</v>
       </c>
       <c r="E64" s="80"/>
@@ -15487,12 +15493,12 @@
       <c r="AB64" s="80"/>
     </row>
     <row r="65" spans="1:28" ht="15">
-      <c r="A65" s="168"/>
-      <c r="B65" s="174" t="s">
+      <c r="A65" s="170"/>
+      <c r="B65" s="165" t="s">
         <v>99</v>
       </c>
-      <c r="C65" s="174"/>
-      <c r="D65" s="81" t="s">
+      <c r="C65" s="165"/>
+      <c r="D65" s="72" t="s">
         <v>234</v>
       </c>
       <c r="E65" s="80"/>
@@ -15521,12 +15527,12 @@
       <c r="AB65" s="80"/>
     </row>
     <row r="66" spans="1:28" ht="15">
-      <c r="A66" s="168"/>
-      <c r="B66" s="174" t="s">
+      <c r="A66" s="170"/>
+      <c r="B66" s="165" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="174"/>
-      <c r="D66" s="81" t="s">
+      <c r="C66" s="165"/>
+      <c r="D66" s="72" t="s">
         <v>235</v>
       </c>
       <c r="E66" s="80"/>
@@ -15555,12 +15561,12 @@
       <c r="AB66" s="80"/>
     </row>
     <row r="67" spans="1:28" ht="15">
-      <c r="A67" s="168"/>
-      <c r="B67" s="174" t="s">
+      <c r="A67" s="170"/>
+      <c r="B67" s="165" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="174"/>
-      <c r="D67" s="81" t="s">
+      <c r="C67" s="165"/>
+      <c r="D67" s="72" t="s">
         <v>236</v>
       </c>
       <c r="E67" s="80"/>
@@ -15589,12 +15595,12 @@
       <c r="AB67" s="80"/>
     </row>
     <row r="68" spans="1:28" ht="15">
-      <c r="A68" s="168"/>
-      <c r="B68" s="174" t="s">
+      <c r="A68" s="170"/>
+      <c r="B68" s="165" t="s">
         <v>105</v>
       </c>
-      <c r="C68" s="174"/>
-      <c r="D68" s="81" t="s">
+      <c r="C68" s="165"/>
+      <c r="D68" s="72" t="s">
         <v>237</v>
       </c>
       <c r="E68" s="80"/>
@@ -15623,14 +15629,14 @@
       <c r="AB68" s="80"/>
     </row>
     <row r="69" spans="1:28" ht="15">
-      <c r="A69" s="168"/>
-      <c r="B69" s="164" t="s">
+      <c r="A69" s="170"/>
+      <c r="B69" s="166" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="72">
         <v>1603</v>
       </c>
-      <c r="D69" s="81" t="s">
+      <c r="D69" s="72" t="s">
         <v>238</v>
       </c>
       <c r="E69" s="80"/>
@@ -15659,12 +15665,12 @@
       <c r="AB69" s="80"/>
     </row>
     <row r="70" spans="1:28" ht="15">
-      <c r="A70" s="168"/>
-      <c r="B70" s="165"/>
+      <c r="A70" s="170"/>
+      <c r="B70" s="167"/>
       <c r="C70" s="72">
         <v>1608</v>
       </c>
-      <c r="D70" s="81" t="s">
+      <c r="D70" s="72" t="s">
         <v>239</v>
       </c>
       <c r="E70" s="80"/>
@@ -15693,12 +15699,12 @@
       <c r="AB70" s="80"/>
     </row>
     <row r="71" spans="1:28" ht="15">
-      <c r="A71" s="168"/>
-      <c r="B71" s="165"/>
+      <c r="A71" s="170"/>
+      <c r="B71" s="167"/>
       <c r="C71" s="72">
         <v>1613</v>
       </c>
-      <c r="D71" s="81" t="s">
+      <c r="D71" s="72" t="s">
         <v>240</v>
       </c>
       <c r="E71" s="80"/>
@@ -15727,12 +15733,12 @@
       <c r="AB71" s="80"/>
     </row>
     <row r="72" spans="1:28" ht="15">
-      <c r="A72" s="168"/>
-      <c r="B72" s="166"/>
+      <c r="A72" s="170"/>
+      <c r="B72" s="168"/>
       <c r="C72" s="72">
         <v>1618</v>
       </c>
-      <c r="D72" s="81" t="s">
+      <c r="D72" s="72" t="s">
         <v>241</v>
       </c>
       <c r="E72" s="80"/>
@@ -15761,14 +15767,14 @@
       <c r="AB72" s="80"/>
     </row>
     <row r="73" spans="1:28" ht="15">
-      <c r="A73" s="168"/>
-      <c r="B73" s="164" t="s">
+      <c r="A73" s="170"/>
+      <c r="B73" s="166" t="s">
         <v>112</v>
       </c>
       <c r="C73" s="72">
         <v>1603</v>
       </c>
-      <c r="D73" s="81" t="s">
+      <c r="D73" s="72" t="s">
         <v>242</v>
       </c>
       <c r="E73" s="80"/>
@@ -15797,12 +15803,12 @@
       <c r="AB73" s="80"/>
     </row>
     <row r="74" spans="1:28" ht="15">
-      <c r="A74" s="168"/>
-      <c r="B74" s="165"/>
+      <c r="A74" s="170"/>
+      <c r="B74" s="167"/>
       <c r="C74" s="72">
         <v>1608</v>
       </c>
-      <c r="D74" s="81" t="s">
+      <c r="D74" s="72" t="s">
         <v>243</v>
       </c>
       <c r="E74" s="80"/>
@@ -15831,12 +15837,12 @@
       <c r="AB74" s="80"/>
     </row>
     <row r="75" spans="1:28" ht="15">
-      <c r="A75" s="168"/>
-      <c r="B75" s="165"/>
+      <c r="A75" s="170"/>
+      <c r="B75" s="167"/>
       <c r="C75" s="72">
         <v>1613</v>
       </c>
-      <c r="D75" s="81" t="s">
+      <c r="D75" s="72" t="s">
         <v>244</v>
       </c>
       <c r="E75" s="80"/>
@@ -15865,12 +15871,12 @@
       <c r="AB75" s="80"/>
     </row>
     <row r="76" spans="1:28" ht="15">
-      <c r="A76" s="168"/>
-      <c r="B76" s="166"/>
+      <c r="A76" s="170"/>
+      <c r="B76" s="168"/>
       <c r="C76" s="72">
         <v>1618</v>
       </c>
-      <c r="D76" s="81" t="s">
+      <c r="D76" s="72" t="s">
         <v>245</v>
       </c>
       <c r="E76" s="80"/>
@@ -15899,12 +15905,12 @@
       <c r="AB76" s="80"/>
     </row>
     <row r="77" spans="1:28" ht="15">
-      <c r="A77" s="168"/>
-      <c r="B77" s="174" t="s">
+      <c r="A77" s="170"/>
+      <c r="B77" s="165" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="174"/>
-      <c r="D77" s="81" t="s">
+      <c r="C77" s="165"/>
+      <c r="D77" s="72" t="s">
         <v>246</v>
       </c>
       <c r="E77" s="80"/>
@@ -15933,12 +15939,12 @@
       <c r="AB77" s="80"/>
     </row>
     <row r="78" spans="1:28" ht="15">
-      <c r="A78" s="168"/>
-      <c r="B78" s="174" t="s">
+      <c r="A78" s="170"/>
+      <c r="B78" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="C78" s="174"/>
-      <c r="D78" s="81" t="s">
+      <c r="C78" s="165"/>
+      <c r="D78" s="72" t="s">
         <v>247</v>
       </c>
       <c r="E78" s="80"/>
@@ -15967,12 +15973,12 @@
       <c r="AB78" s="80"/>
     </row>
     <row r="79" spans="1:28" ht="15">
-      <c r="A79" s="168"/>
-      <c r="B79" s="174" t="s">
+      <c r="A79" s="170"/>
+      <c r="B79" s="165" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="174"/>
-      <c r="D79" s="81" t="s">
+      <c r="C79" s="165"/>
+      <c r="D79" s="72" t="s">
         <v>248</v>
       </c>
       <c r="E79" s="80"/>
@@ -16001,12 +16007,12 @@
       <c r="AB79" s="80"/>
     </row>
     <row r="80" spans="1:28" ht="15">
-      <c r="A80" s="169"/>
-      <c r="B80" s="174" t="s">
+      <c r="A80" s="171"/>
+      <c r="B80" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="C80" s="174"/>
-      <c r="D80" s="81" t="s">
+      <c r="C80" s="165"/>
+      <c r="D80" s="72" t="s">
         <v>249</v>
       </c>
       <c r="E80" s="80"/>
@@ -16035,16 +16041,16 @@
       <c r="AB80" s="80"/>
     </row>
     <row r="81" spans="1:28" ht="15">
-      <c r="A81" s="164" t="s">
+      <c r="A81" s="166" t="s">
         <v>121</v>
       </c>
-      <c r="B81" s="164" t="s">
+      <c r="B81" s="166" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="D81" s="81" t="s">
+      <c r="D81" s="72" t="s">
         <v>250</v>
       </c>
       <c r="E81" s="80"/>
@@ -16073,12 +16079,12 @@
       <c r="AB81" s="80"/>
     </row>
     <row r="82" spans="1:28" ht="15">
-      <c r="A82" s="165"/>
-      <c r="B82" s="165"/>
+      <c r="A82" s="167"/>
+      <c r="B82" s="167"/>
       <c r="C82" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="D82" s="81" t="s">
+      <c r="D82" s="72" t="s">
         <v>251</v>
       </c>
       <c r="E82" s="80"/>
@@ -16107,12 +16113,12 @@
       <c r="AB82" s="80"/>
     </row>
     <row r="83" spans="1:28" ht="15">
-      <c r="A83" s="165"/>
-      <c r="B83" s="165"/>
+      <c r="A83" s="167"/>
+      <c r="B83" s="167"/>
       <c r="C83" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="D83" s="81" t="s">
+      <c r="D83" s="72" t="s">
         <v>252</v>
       </c>
       <c r="E83" s="80"/>
@@ -16141,12 +16147,12 @@
       <c r="AB83" s="80"/>
     </row>
     <row r="84" spans="1:28" ht="30">
-      <c r="A84" s="165"/>
-      <c r="B84" s="165"/>
+      <c r="A84" s="167"/>
+      <c r="B84" s="167"/>
       <c r="C84" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="D84" s="81" t="s">
+      <c r="D84" s="72" t="s">
         <v>253</v>
       </c>
       <c r="E84" s="80"/>
@@ -16175,12 +16181,12 @@
       <c r="AB84" s="80"/>
     </row>
     <row r="85" spans="1:28" ht="15">
-      <c r="A85" s="165"/>
-      <c r="B85" s="165"/>
+      <c r="A85" s="167"/>
+      <c r="B85" s="167"/>
       <c r="C85" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="D85" s="81" t="s">
+      <c r="D85" s="72" t="s">
         <v>254</v>
       </c>
       <c r="E85" s="80"/>
@@ -16209,12 +16215,12 @@
       <c r="AB85" s="80"/>
     </row>
     <row r="86" spans="1:28" ht="15">
-      <c r="A86" s="165"/>
-      <c r="B86" s="165"/>
+      <c r="A86" s="167"/>
+      <c r="B86" s="167"/>
       <c r="C86" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="D86" s="81" t="s">
+      <c r="D86" s="72" t="s">
         <v>255</v>
       </c>
       <c r="E86" s="80"/>
@@ -16243,12 +16249,12 @@
       <c r="AB86" s="80"/>
     </row>
     <row r="87" spans="1:28" ht="15">
-      <c r="A87" s="165"/>
-      <c r="B87" s="165"/>
+      <c r="A87" s="167"/>
+      <c r="B87" s="167"/>
       <c r="C87" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="D87" s="81" t="s">
+      <c r="D87" s="72" t="s">
         <v>256</v>
       </c>
       <c r="E87" s="80"/>
@@ -16277,12 +16283,12 @@
       <c r="AB87" s="80"/>
     </row>
     <row r="88" spans="1:28" ht="15">
-      <c r="A88" s="165"/>
-      <c r="B88" s="166"/>
+      <c r="A88" s="167"/>
+      <c r="B88" s="168"/>
       <c r="C88" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D88" s="81" t="s">
+      <c r="D88" s="72" t="s">
         <v>257</v>
       </c>
       <c r="E88" s="80"/>
@@ -16311,14 +16317,14 @@
       <c r="AB88" s="80"/>
     </row>
     <row r="89" spans="1:28" ht="30">
-      <c r="A89" s="165"/>
-      <c r="B89" s="167" t="s">
+      <c r="A89" s="167"/>
+      <c r="B89" s="169" t="s">
         <v>130</v>
       </c>
       <c r="C89" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="D89" s="81" t="s">
+      <c r="D89" s="72" t="s">
         <v>258</v>
       </c>
       <c r="E89" s="80"/>
@@ -16347,12 +16353,12 @@
       <c r="AB89" s="80"/>
     </row>
     <row r="90" spans="1:28" ht="15">
-      <c r="A90" s="165"/>
-      <c r="B90" s="168"/>
+      <c r="A90" s="167"/>
+      <c r="B90" s="170"/>
       <c r="C90" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="D90" s="81" t="s">
+      <c r="D90" s="72" t="s">
         <v>259</v>
       </c>
       <c r="E90" s="80"/>
@@ -16381,12 +16387,12 @@
       <c r="AB90" s="80"/>
     </row>
     <row r="91" spans="1:28" ht="15">
-      <c r="A91" s="165"/>
-      <c r="B91" s="168"/>
+      <c r="A91" s="167"/>
+      <c r="B91" s="170"/>
       <c r="C91" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="D91" s="81" t="s">
+      <c r="D91" s="72" t="s">
         <v>260</v>
       </c>
       <c r="E91" s="80"/>
@@ -16415,12 +16421,12 @@
       <c r="AB91" s="80"/>
     </row>
     <row r="92" spans="1:28" ht="15">
-      <c r="A92" s="165"/>
-      <c r="B92" s="168"/>
+      <c r="A92" s="167"/>
+      <c r="B92" s="170"/>
       <c r="C92" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="D92" s="81" t="s">
+      <c r="D92" s="72" t="s">
         <v>261</v>
       </c>
       <c r="E92" s="80"/>
@@ -16449,17 +16455,15 @@
       <c r="AB92" s="80"/>
     </row>
     <row r="93" spans="1:28" ht="15">
-      <c r="A93" s="165"/>
-      <c r="B93" s="169"/>
+      <c r="A93" s="167"/>
+      <c r="B93" s="171"/>
       <c r="C93" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D93" s="81" t="s">
+      <c r="D93" s="72" t="s">
         <v>262</v>
       </c>
-      <c r="E93" s="80">
-        <v>1</v>
-      </c>
+      <c r="E93" s="80"/>
       <c r="F93" s="80"/>
       <c r="G93" s="80"/>
       <c r="H93" s="80"/>
@@ -16485,14 +16489,14 @@
       <c r="AB93" s="80"/>
     </row>
     <row r="94" spans="1:28" ht="15">
-      <c r="A94" s="165"/>
-      <c r="B94" s="164" t="s">
+      <c r="A94" s="167"/>
+      <c r="B94" s="166" t="s">
         <v>132</v>
       </c>
       <c r="C94" s="72">
         <v>1603</v>
       </c>
-      <c r="D94" s="81"/>
+      <c r="D94" s="72"/>
       <c r="E94" s="80"/>
       <c r="F94" s="80"/>
       <c r="G94" s="80"/>
@@ -16519,12 +16523,12 @@
       <c r="AB94" s="80"/>
     </row>
     <row r="95" spans="1:28" ht="15">
-      <c r="A95" s="165"/>
-      <c r="B95" s="165"/>
+      <c r="A95" s="167"/>
+      <c r="B95" s="167"/>
       <c r="C95" s="72">
         <v>1608</v>
       </c>
-      <c r="D95" s="81"/>
+      <c r="D95" s="72"/>
       <c r="E95" s="80"/>
       <c r="F95" s="80"/>
       <c r="G95" s="80"/>
@@ -16551,12 +16555,12 @@
       <c r="AB95" s="80"/>
     </row>
     <row r="96" spans="1:28" ht="15">
-      <c r="A96" s="165"/>
-      <c r="B96" s="165"/>
+      <c r="A96" s="167"/>
+      <c r="B96" s="167"/>
       <c r="C96" s="72">
         <v>1613</v>
       </c>
-      <c r="D96" s="81"/>
+      <c r="D96" s="72"/>
       <c r="E96" s="80"/>
       <c r="F96" s="80"/>
       <c r="G96" s="80"/>
@@ -16583,12 +16587,12 @@
       <c r="AB96" s="80"/>
     </row>
     <row r="97" spans="1:28" ht="15">
-      <c r="A97" s="166"/>
-      <c r="B97" s="166"/>
+      <c r="A97" s="168"/>
+      <c r="B97" s="168"/>
       <c r="C97" s="72">
         <v>1618</v>
       </c>
-      <c r="D97" s="81"/>
+      <c r="D97" s="72"/>
       <c r="E97" s="80"/>
       <c r="F97" s="80"/>
       <c r="G97" s="80"/>
@@ -16615,14 +16619,12 @@
       <c r="AB97" s="80"/>
     </row>
     <row r="98" spans="1:28" ht="15">
-      <c r="A98" s="170" t="s">
+      <c r="A98" s="159" t="s">
         <v>173</v>
       </c>
-      <c r="B98" s="177"/>
-      <c r="C98" s="171"/>
-      <c r="D98" s="81" t="s">
-        <v>220</v>
-      </c>
+      <c r="B98" s="160"/>
+      <c r="C98" s="161"/>
+      <c r="D98" s="72"/>
       <c r="E98" s="80"/>
       <c r="F98" s="80"/>
       <c r="G98" s="80"/>
@@ -16649,14 +16651,12 @@
       <c r="AB98" s="80"/>
     </row>
     <row r="99" spans="1:28" ht="15">
-      <c r="A99" s="170" t="s">
+      <c r="A99" s="159" t="s">
         <v>174</v>
       </c>
-      <c r="B99" s="177"/>
-      <c r="C99" s="171"/>
-      <c r="D99" s="81" t="s">
-        <v>209</v>
-      </c>
+      <c r="B99" s="160"/>
+      <c r="C99" s="161"/>
+      <c r="D99" s="72"/>
       <c r="E99" s="80"/>
       <c r="F99" s="80"/>
       <c r="G99" s="80"/>
@@ -16683,17 +16683,15 @@
       <c r="AB99" s="80"/>
     </row>
     <row r="100" spans="1:28" ht="15">
-      <c r="A100" s="178" t="s">
+      <c r="A100" s="162" t="s">
         <v>135</v>
       </c>
-      <c r="B100" s="179"/>
-      <c r="C100" s="180"/>
-      <c r="D100" s="81" t="s">
+      <c r="B100" s="163"/>
+      <c r="C100" s="164"/>
+      <c r="D100" s="72" t="s">
         <v>263</v>
       </c>
-      <c r="E100" s="80">
-        <v>1</v>
-      </c>
+      <c r="E100" s="80"/>
       <c r="F100" s="80"/>
       <c r="G100" s="80"/>
       <c r="H100" s="80"/>
@@ -16720,22 +16718,32 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="A81:A97"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="D2:P3"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="A6:A39"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B19:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B57:C57"/>
@@ -16752,32 +16760,22 @@
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="Q1:T1"/>
-    <mergeCell ref="D2:P3"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="A6:A39"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="B19:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="A81:A97"/>
+    <mergeCell ref="B81:B88"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="B94:B97"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16824,22 +16822,22 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="126"/>
-      <c r="U3" s="126"/>
-      <c r="V3" s="126"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="121"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="121"/>
+      <c r="U3" s="121"/>
+      <c r="V3" s="121"/>
     </row>
     <row r="4" spans="1:223" ht="22.5">
       <c r="A4" s="8"/>
@@ -16847,19 +16845,19 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="127" t="s">
+      <c r="F4" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="127"/>
-      <c r="P4" s="127"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
@@ -16874,33 +16872,33 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
     </row>
     <row r="6" spans="1:223" s="17" customFormat="1" ht="33">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="130" t="s">
+      <c r="B6" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="132"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
       <c r="F6" s="10" t="s">
         <v>146</v>
       </c>
@@ -16922,12 +16920,12 @@
       <c r="L6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="130" t="s">
+      <c r="M6" s="125" t="s">
         <v>152</v>
       </c>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="132"/>
+      <c r="N6" s="126"/>
+      <c r="O6" s="126"/>
+      <c r="P6" s="127"/>
       <c r="Q6" s="10" t="s">
         <v>146</v>
       </c>
@@ -16948,14 +16946,14 @@
       </c>
     </row>
     <row r="7" spans="1:223" s="1" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="100" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="135"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="103"/>
       <c r="E7" s="18">
         <v>5404</v>
       </c>
@@ -16983,14 +16981,14 @@
         <f>Sheet1!P7</f>
         <v>0</v>
       </c>
-      <c r="L7" s="186" t="s">
+      <c r="L7" s="191" t="s">
         <v>47</v>
       </c>
-      <c r="M7" s="118" t="s">
+      <c r="M7" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
       <c r="P7" s="30" t="s">
         <v>49</v>
       </c>
@@ -17221,10 +17219,10 @@
       <c r="HO7" s="3"/>
     </row>
     <row r="8" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A8" s="94"/>
-      <c r="B8" s="139"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="141"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
       <c r="E8" s="18">
         <v>5408</v>
       </c>
@@ -17252,12 +17250,12 @@
         <f>Sheet1!P8</f>
         <v>0</v>
       </c>
-      <c r="L8" s="187"/>
-      <c r="M8" s="118" t="s">
+      <c r="L8" s="192"/>
+      <c r="M8" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
       <c r="P8" s="30" t="s">
         <v>51</v>
       </c>
@@ -17287,10 +17285,10 @@
       </c>
     </row>
     <row r="9" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A9" s="94"/>
-      <c r="B9" s="139"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="141"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="106"/>
       <c r="E9" s="18">
         <v>5414</v>
       </c>
@@ -17318,12 +17316,12 @@
         <f>Sheet1!P9</f>
         <v>0</v>
       </c>
-      <c r="L9" s="187"/>
-      <c r="M9" s="118" t="s">
+      <c r="L9" s="192"/>
+      <c r="M9" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="110"/>
       <c r="P9" s="30" t="s">
         <v>53</v>
       </c>
@@ -17353,10 +17351,10 @@
       </c>
     </row>
     <row r="10" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A10" s="94"/>
-      <c r="B10" s="136"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="138"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="109"/>
       <c r="E10" s="18">
         <v>5418</v>
       </c>
@@ -17384,12 +17382,12 @@
         <f>Sheet1!P10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="187"/>
-      <c r="M10" s="118" t="s">
+      <c r="L10" s="192"/>
+      <c r="M10" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="125"/>
-      <c r="O10" s="125"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
       <c r="P10" s="30" t="s">
         <v>55</v>
       </c>
@@ -17419,12 +17417,12 @@
       </c>
     </row>
     <row r="11" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A11" s="94"/>
-      <c r="B11" s="133" t="s">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="135"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="103"/>
       <c r="E11" s="18">
         <v>4405</v>
       </c>
@@ -17452,12 +17450,12 @@
         <f>Sheet1!P11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="187"/>
-      <c r="M11" s="118" t="s">
+      <c r="L11" s="192"/>
+      <c r="M11" s="119" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="125"/>
-      <c r="O11" s="125"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="110"/>
       <c r="P11" s="30" t="s">
         <v>57</v>
       </c>
@@ -17487,10 +17485,10 @@
       </c>
     </row>
     <row r="12" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A12" s="94"/>
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="141"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="18">
         <v>4412</v>
       </c>
@@ -17518,12 +17516,12 @@
         <f>Sheet1!P12</f>
         <v>0</v>
       </c>
-      <c r="L12" s="187"/>
-      <c r="M12" s="118" t="s">
+      <c r="L12" s="192"/>
+      <c r="M12" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="N12" s="125"/>
-      <c r="O12" s="125"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="110"/>
       <c r="P12" s="30" t="s">
         <v>59</v>
       </c>
@@ -17553,10 +17551,10 @@
       </c>
     </row>
     <row r="13" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A13" s="94"/>
-      <c r="B13" s="136"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="138"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
       <c r="E13" s="18">
         <v>4420</v>
       </c>
@@ -17584,12 +17582,12 @@
         <f>Sheet1!P13</f>
         <v>0</v>
       </c>
-      <c r="L13" s="187"/>
-      <c r="M13" s="118" t="s">
+      <c r="L13" s="192"/>
+      <c r="M13" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="125"/>
-      <c r="O13" s="125"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="110"/>
       <c r="P13" s="30" t="s">
         <v>61</v>
       </c>
@@ -17619,12 +17617,12 @@
       </c>
     </row>
     <row r="14" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A14" s="94"/>
-      <c r="B14" s="133" t="s">
+      <c r="A14" s="100"/>
+      <c r="B14" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="135"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="103"/>
       <c r="E14" s="18">
         <v>4402</v>
       </c>
@@ -17652,12 +17650,12 @@
         <f>Sheet1!P14</f>
         <v>0</v>
       </c>
-      <c r="L14" s="187"/>
-      <c r="M14" s="118" t="s">
+      <c r="L14" s="192"/>
+      <c r="M14" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="110"/>
       <c r="P14" s="30" t="s">
         <v>63</v>
       </c>
@@ -17687,10 +17685,10 @@
       </c>
     </row>
     <row r="15" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A15" s="94"/>
-      <c r="B15" s="139"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="141"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="18">
         <v>4405</v>
       </c>
@@ -17718,12 +17716,12 @@
         <f>Sheet1!P15</f>
         <v>0</v>
       </c>
-      <c r="L15" s="187"/>
-      <c r="M15" s="118" t="s">
+      <c r="L15" s="192"/>
+      <c r="M15" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="110"/>
       <c r="P15" s="30" t="s">
         <v>65</v>
       </c>
@@ -17753,10 +17751,10 @@
       </c>
     </row>
     <row r="16" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A16" s="94"/>
-      <c r="B16" s="139"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="141"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="106"/>
       <c r="E16" s="18">
         <v>4409</v>
       </c>
@@ -17784,12 +17782,12 @@
         <f>Sheet1!P16</f>
         <v>0</v>
       </c>
-      <c r="L16" s="187"/>
-      <c r="M16" s="118" t="s">
+      <c r="L16" s="192"/>
+      <c r="M16" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="N16" s="125"/>
-      <c r="O16" s="125"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
       <c r="P16" s="30" t="s">
         <v>67</v>
       </c>
@@ -17819,10 +17817,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A17" s="94"/>
-      <c r="B17" s="139"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="141"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="104"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="106"/>
       <c r="E17" s="18">
         <v>4412</v>
       </c>
@@ -17850,12 +17848,12 @@
         <f>Sheet1!P17</f>
         <v>0</v>
       </c>
-      <c r="L17" s="187"/>
-      <c r="M17" s="118" t="s">
+      <c r="L17" s="192"/>
+      <c r="M17" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="N17" s="125"/>
-      <c r="O17" s="125"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="110"/>
       <c r="P17" s="30" t="s">
         <v>69</v>
       </c>
@@ -17885,10 +17883,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A18" s="94"/>
-      <c r="B18" s="139"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="141"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="104"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="106"/>
       <c r="E18" s="18">
         <v>4415</v>
       </c>
@@ -17916,12 +17914,12 @@
         <f>Sheet1!P18</f>
         <v>0</v>
       </c>
-      <c r="L18" s="187"/>
-      <c r="M18" s="118" t="s">
+      <c r="L18" s="192"/>
+      <c r="M18" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="N18" s="125"/>
-      <c r="O18" s="125"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
       <c r="P18" s="30" t="s">
         <v>71</v>
       </c>
@@ -17951,10 +17949,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A19" s="94"/>
-      <c r="B19" s="139"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="141"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="26">
         <v>4419</v>
       </c>
@@ -17982,12 +17980,12 @@
         <f>Sheet1!P19</f>
         <v>0</v>
       </c>
-      <c r="L19" s="187"/>
-      <c r="M19" s="118" t="s">
+      <c r="L19" s="192"/>
+      <c r="M19" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="N19" s="125"/>
-      <c r="O19" s="125"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="110"/>
       <c r="P19" s="28" t="s">
         <v>73</v>
       </c>
@@ -18017,12 +18015,12 @@
       </c>
     </row>
     <row r="20" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A20" s="94"/>
-      <c r="B20" s="133" t="s">
+      <c r="A20" s="100"/>
+      <c r="B20" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="134"/>
-      <c r="D20" s="135"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="103"/>
       <c r="E20" s="18">
         <v>3201</v>
       </c>
@@ -18050,12 +18048,12 @@
         <f>Sheet1!P20</f>
         <v>0</v>
       </c>
-      <c r="L20" s="187"/>
-      <c r="M20" s="118" t="s">
+      <c r="L20" s="192"/>
+      <c r="M20" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="N20" s="125"/>
-      <c r="O20" s="125"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="110"/>
       <c r="P20" s="30" t="s">
         <v>75</v>
       </c>
@@ -18085,10 +18083,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A21" s="94"/>
-      <c r="B21" s="139"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="141"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="106"/>
       <c r="E21" s="18">
         <v>3203</v>
       </c>
@@ -18116,12 +18114,12 @@
         <f>Sheet1!P21</f>
         <v>0</v>
       </c>
-      <c r="L21" s="187"/>
-      <c r="M21" s="118" t="s">
+      <c r="L21" s="192"/>
+      <c r="M21" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="N21" s="125"/>
-      <c r="O21" s="125"/>
+      <c r="N21" s="110"/>
+      <c r="O21" s="110"/>
       <c r="P21" s="30" t="s">
         <v>77</v>
       </c>
@@ -18151,10 +18149,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A22" s="94"/>
-      <c r="B22" s="139"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="141"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="104"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="106"/>
       <c r="E22" s="17">
         <v>3206</v>
       </c>
@@ -18182,12 +18180,12 @@
         <f>Sheet1!P22</f>
         <v>0</v>
       </c>
-      <c r="L22" s="187"/>
-      <c r="M22" s="118" t="s">
+      <c r="L22" s="192"/>
+      <c r="M22" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="N22" s="125"/>
-      <c r="O22" s="125"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="110"/>
       <c r="P22" s="30" t="s">
         <v>79</v>
       </c>
@@ -18217,10 +18215,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A23" s="94"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="106"/>
       <c r="E23" s="18">
         <v>3208</v>
       </c>
@@ -18248,12 +18246,12 @@
         <f>Sheet1!P23</f>
         <v>0</v>
       </c>
-      <c r="L23" s="187"/>
-      <c r="M23" s="118" t="s">
+      <c r="L23" s="192"/>
+      <c r="M23" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="N23" s="125"/>
-      <c r="O23" s="125"/>
+      <c r="N23" s="110"/>
+      <c r="O23" s="110"/>
       <c r="P23" s="17" t="s">
         <v>81</v>
       </c>
@@ -18283,10 +18281,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A24" s="94"/>
-      <c r="B24" s="139"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="141"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="106"/>
       <c r="E24" s="18">
         <v>3211</v>
       </c>
@@ -18314,12 +18312,12 @@
         <f>Sheet1!P24</f>
         <v>0</v>
       </c>
-      <c r="L24" s="187"/>
-      <c r="M24" s="118" t="s">
+      <c r="L24" s="192"/>
+      <c r="M24" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="N24" s="125"/>
-      <c r="O24" s="125"/>
+      <c r="N24" s="110"/>
+      <c r="O24" s="110"/>
       <c r="P24" s="30" t="s">
         <v>83</v>
       </c>
@@ -18349,10 +18347,10 @@
       </c>
     </row>
     <row r="25" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A25" s="94"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="141"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="106"/>
       <c r="E25" s="18">
         <v>3213</v>
       </c>
@@ -18380,12 +18378,12 @@
         <f>Sheet1!P25</f>
         <v>0</v>
       </c>
-      <c r="L25" s="188"/>
-      <c r="M25" s="118" t="s">
+      <c r="L25" s="193"/>
+      <c r="M25" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="N25" s="125"/>
-      <c r="O25" s="125"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="110"/>
       <c r="P25" s="30" t="s">
         <v>85</v>
       </c>
@@ -18415,10 +18413,10 @@
       </c>
     </row>
     <row r="26" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A26" s="94"/>
-      <c r="B26" s="139"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="141"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="106"/>
       <c r="E26" s="18">
         <v>3216</v>
       </c>
@@ -18446,14 +18444,14 @@
         <f>Sheet1!P26</f>
         <v>0</v>
       </c>
-      <c r="L26" s="184" t="s">
+      <c r="L26" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="M26" s="116" t="s">
+      <c r="M26" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="N26" s="117"/>
-      <c r="O26" s="118"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="119"/>
       <c r="P26" s="28" t="s">
         <v>88</v>
       </c>
@@ -18483,10 +18481,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A27" s="94"/>
-      <c r="B27" s="136"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="138"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
       <c r="E27" s="18">
         <v>3218</v>
       </c>
@@ -18514,12 +18512,12 @@
         <f>Sheet1!P27</f>
         <v>0</v>
       </c>
-      <c r="L27" s="184"/>
-      <c r="M27" s="116" t="s">
+      <c r="L27" s="197"/>
+      <c r="M27" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="N27" s="117"/>
-      <c r="O27" s="118"/>
+      <c r="N27" s="118"/>
+      <c r="O27" s="119"/>
       <c r="P27" s="28" t="s">
         <v>90</v>
       </c>
@@ -18549,12 +18547,12 @@
       </c>
     </row>
     <row r="28" spans="1:22" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="133" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="134"/>
-      <c r="D28" s="135"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103"/>
       <c r="E28" s="18">
         <v>1808</v>
       </c>
@@ -18582,12 +18580,12 @@
         <f>Sheet1!P28</f>
         <v>0</v>
       </c>
-      <c r="L28" s="184"/>
-      <c r="M28" s="116" t="s">
+      <c r="L28" s="197"/>
+      <c r="M28" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="N28" s="117"/>
-      <c r="O28" s="118"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="119"/>
       <c r="P28" s="28" t="s">
         <v>92</v>
       </c>
@@ -18617,10 +18615,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A29" s="94"/>
-      <c r="B29" s="136"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="138"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="107"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109"/>
       <c r="E29" s="18">
         <v>1818</v>
       </c>
@@ -18648,12 +18646,12 @@
         <f>Sheet1!P29</f>
         <v>0</v>
       </c>
-      <c r="L29" s="184"/>
-      <c r="M29" s="116" t="s">
+      <c r="L29" s="197"/>
+      <c r="M29" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="N29" s="117"/>
-      <c r="O29" s="118"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="119"/>
       <c r="P29" s="28" t="s">
         <v>94</v>
       </c>
@@ -18683,12 +18681,12 @@
       </c>
     </row>
     <row r="30" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A30" s="94"/>
-      <c r="B30" s="133" t="s">
+      <c r="A30" s="100"/>
+      <c r="B30" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="135"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
       <c r="E30" s="18">
         <v>1403</v>
       </c>
@@ -18716,12 +18714,12 @@
         <f>Sheet1!P30</f>
         <v>0</v>
       </c>
-      <c r="L30" s="184"/>
-      <c r="M30" s="116" t="s">
+      <c r="L30" s="197"/>
+      <c r="M30" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="N30" s="117"/>
-      <c r="O30" s="118"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="119"/>
       <c r="P30" s="28" t="s">
         <v>96</v>
       </c>
@@ -18751,10 +18749,10 @@
       </c>
     </row>
     <row r="31" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A31" s="94"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="141"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="106"/>
       <c r="E31" s="18">
         <v>1408</v>
       </c>
@@ -18782,12 +18780,12 @@
         <f>Sheet1!P31</f>
         <v>0</v>
       </c>
-      <c r="L31" s="184"/>
-      <c r="M31" s="116" t="s">
+      <c r="L31" s="197"/>
+      <c r="M31" s="117" t="s">
         <v>97</v>
       </c>
-      <c r="N31" s="117"/>
-      <c r="O31" s="118"/>
+      <c r="N31" s="118"/>
+      <c r="O31" s="119"/>
       <c r="P31" s="28" t="s">
         <v>98</v>
       </c>
@@ -18817,10 +18815,10 @@
       </c>
     </row>
     <row r="32" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A32" s="94"/>
-      <c r="B32" s="139"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="141"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="106"/>
       <c r="E32" s="18">
         <v>1413</v>
       </c>
@@ -18848,12 +18846,12 @@
         <f>Sheet1!P32</f>
         <v>0</v>
       </c>
-      <c r="L32" s="184"/>
-      <c r="M32" s="116" t="s">
+      <c r="L32" s="197"/>
+      <c r="M32" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="N32" s="117"/>
-      <c r="O32" s="118"/>
+      <c r="N32" s="118"/>
+      <c r="O32" s="119"/>
       <c r="P32" s="28" t="s">
         <v>100</v>
       </c>
@@ -18883,10 +18881,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A33" s="94"/>
-      <c r="B33" s="136"/>
-      <c r="C33" s="137"/>
-      <c r="D33" s="138"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="109"/>
       <c r="E33" s="18">
         <v>1418</v>
       </c>
@@ -18914,12 +18912,12 @@
         <f>Sheet1!P33</f>
         <v>0</v>
       </c>
-      <c r="L33" s="184"/>
-      <c r="M33" s="116" t="s">
+      <c r="L33" s="197"/>
+      <c r="M33" s="117" t="s">
         <v>101</v>
       </c>
-      <c r="N33" s="117"/>
-      <c r="O33" s="118"/>
+      <c r="N33" s="118"/>
+      <c r="O33" s="119"/>
       <c r="P33" s="28" t="s">
         <v>102</v>
       </c>
@@ -18949,12 +18947,12 @@
       </c>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A34" s="94"/>
-      <c r="B34" s="145" t="s">
+      <c r="A34" s="100"/>
+      <c r="B34" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="146"/>
-      <c r="D34" s="147"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="96"/>
       <c r="E34" s="18">
         <v>4311</v>
       </c>
@@ -18982,12 +18980,12 @@
         <f>Sheet1!P34</f>
         <v>0</v>
       </c>
-      <c r="L34" s="184"/>
-      <c r="M34" s="116" t="s">
+      <c r="L34" s="197"/>
+      <c r="M34" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="N34" s="117"/>
-      <c r="O34" s="118"/>
+      <c r="N34" s="118"/>
+      <c r="O34" s="119"/>
       <c r="P34" s="28" t="s">
         <v>104</v>
       </c>
@@ -19017,11 +19015,11 @@
       </c>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A35" s="94"/>
-      <c r="B35" s="119" t="s">
+      <c r="A35" s="100"/>
+      <c r="B35" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="120"/>
+      <c r="C35" s="112"/>
       <c r="D35" s="13" t="s">
         <v>38</v>
       </c>
@@ -19050,12 +19048,12 @@
         <f>Sheet1!P35</f>
         <v>0</v>
       </c>
-      <c r="L35" s="184"/>
-      <c r="M35" s="116" t="s">
+      <c r="L35" s="197"/>
+      <c r="M35" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="N35" s="117"/>
-      <c r="O35" s="118"/>
+      <c r="N35" s="118"/>
+      <c r="O35" s="119"/>
       <c r="P35" s="28" t="s">
         <v>106</v>
       </c>
@@ -19085,9 +19083,9 @@
       </c>
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A36" s="94"/>
-      <c r="B36" s="121"/>
-      <c r="C36" s="122"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="113"/>
+      <c r="C36" s="114"/>
       <c r="D36" s="13" t="s">
         <v>39</v>
       </c>
@@ -19116,11 +19114,11 @@
         <f>Sheet1!P36</f>
         <v>0</v>
       </c>
-      <c r="L36" s="184"/>
-      <c r="M36" s="119" t="s">
+      <c r="L36" s="197"/>
+      <c r="M36" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="N36" s="120"/>
+      <c r="N36" s="112"/>
       <c r="O36" s="18">
         <v>1603</v>
       </c>
@@ -19153,9 +19151,9 @@
       </c>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A37" s="94"/>
-      <c r="B37" s="123"/>
-      <c r="C37" s="124"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="13" t="s">
         <v>40</v>
       </c>
@@ -19184,9 +19182,9 @@
         <f>Sheet1!P37</f>
         <v>0</v>
       </c>
-      <c r="L37" s="184"/>
-      <c r="M37" s="121"/>
-      <c r="N37" s="122"/>
+      <c r="L37" s="197"/>
+      <c r="M37" s="113"/>
+      <c r="N37" s="114"/>
       <c r="O37" s="18">
         <v>1608</v>
       </c>
@@ -19219,12 +19217,12 @@
       </c>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A38" s="94"/>
-      <c r="B38" s="116" t="s">
+      <c r="A38" s="100"/>
+      <c r="B38" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="117"/>
-      <c r="D38" s="118"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
       <c r="E38" s="18"/>
       <c r="F38" s="25">
         <f>Sheet1!F38</f>
@@ -19250,9 +19248,9 @@
         <f>Sheet1!P38</f>
         <v>0</v>
       </c>
-      <c r="L38" s="184"/>
-      <c r="M38" s="121"/>
-      <c r="N38" s="122"/>
+      <c r="L38" s="197"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="114"/>
       <c r="O38" s="18">
         <v>1613</v>
       </c>
@@ -19285,11 +19283,11 @@
       </c>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A39" s="94"/>
-      <c r="B39" s="125" t="s">
+      <c r="A39" s="100"/>
+      <c r="B39" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="125"/>
+      <c r="C39" s="110"/>
       <c r="D39" s="15" t="s">
         <v>43</v>
       </c>
@@ -19320,9 +19318,9 @@
         <f>Sheet1!P39</f>
         <v>0</v>
       </c>
-      <c r="L39" s="184"/>
-      <c r="M39" s="123"/>
-      <c r="N39" s="124"/>
+      <c r="L39" s="197"/>
+      <c r="M39" s="115"/>
+      <c r="N39" s="116"/>
       <c r="O39" s="18">
         <v>1618</v>
       </c>
@@ -19355,9 +19353,9 @@
       </c>
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A40" s="94"/>
-      <c r="B40" s="125"/>
-      <c r="C40" s="125"/>
+      <c r="A40" s="100"/>
+      <c r="B40" s="110"/>
+      <c r="C40" s="110"/>
       <c r="D40" s="15" t="s">
         <v>45</v>
       </c>
@@ -19388,11 +19386,11 @@
         <f>Sheet1!P40</f>
         <v>0</v>
       </c>
-      <c r="L40" s="184"/>
-      <c r="M40" s="119" t="s">
+      <c r="L40" s="197"/>
+      <c r="M40" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="N40" s="120"/>
+      <c r="N40" s="112"/>
       <c r="O40" s="18">
         <v>1603</v>
       </c>
@@ -19425,26 +19423,26 @@
       </c>
     </row>
     <row r="41" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A41" s="194" t="s">
+      <c r="A41" s="185" t="s">
         <v>154</v>
       </c>
-      <c r="B41" s="195" t="s">
+      <c r="B41" s="186" t="s">
         <v>155</v>
       </c>
-      <c r="C41" s="196"/>
-      <c r="D41" s="196"/>
-      <c r="E41" s="196"/>
-      <c r="F41" s="196"/>
-      <c r="G41" s="113" t="s">
+      <c r="C41" s="187"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="146" t="s">
         <v>130</v>
       </c>
-      <c r="H41" s="113"/>
-      <c r="I41" s="113"/>
-      <c r="J41" s="113"/>
-      <c r="K41" s="113"/>
-      <c r="L41" s="184"/>
-      <c r="M41" s="121"/>
-      <c r="N41" s="122"/>
+      <c r="H41" s="146"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="113"/>
+      <c r="N41" s="114"/>
       <c r="O41" s="18">
         <v>1608</v>
       </c>
@@ -19477,20 +19475,20 @@
       </c>
     </row>
     <row r="42" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A42" s="194"/>
-      <c r="B42" s="197"/>
-      <c r="C42" s="198"/>
-      <c r="D42" s="198"/>
-      <c r="E42" s="198"/>
-      <c r="F42" s="198"/>
-      <c r="G42" s="113"/>
-      <c r="H42" s="113"/>
-      <c r="I42" s="113"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="113"/>
-      <c r="L42" s="184"/>
-      <c r="M42" s="121"/>
-      <c r="N42" s="122"/>
+      <c r="A42" s="185"/>
+      <c r="B42" s="188"/>
+      <c r="C42" s="189"/>
+      <c r="D42" s="189"/>
+      <c r="E42" s="189"/>
+      <c r="F42" s="189"/>
+      <c r="G42" s="146"/>
+      <c r="H42" s="146"/>
+      <c r="I42" s="146"/>
+      <c r="J42" s="146"/>
+      <c r="K42" s="146"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="113"/>
+      <c r="N42" s="114"/>
       <c r="O42" s="18">
         <v>1613</v>
       </c>
@@ -19523,20 +19521,20 @@
       </c>
     </row>
     <row r="43" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A43" s="194"/>
-      <c r="B43" s="114"/>
-      <c r="C43" s="199"/>
-      <c r="D43" s="199"/>
-      <c r="E43" s="199"/>
-      <c r="F43" s="199"/>
-      <c r="G43" s="113"/>
-      <c r="H43" s="113"/>
-      <c r="I43" s="113"/>
-      <c r="J43" s="113"/>
-      <c r="K43" s="113"/>
-      <c r="L43" s="184"/>
-      <c r="M43" s="123"/>
-      <c r="N43" s="124"/>
+      <c r="A43" s="185"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="190"/>
+      <c r="D43" s="190"/>
+      <c r="E43" s="190"/>
+      <c r="F43" s="190"/>
+      <c r="G43" s="146"/>
+      <c r="H43" s="146"/>
+      <c r="I43" s="146"/>
+      <c r="J43" s="146"/>
+      <c r="K43" s="146"/>
+      <c r="L43" s="197"/>
+      <c r="M43" s="115"/>
+      <c r="N43" s="116"/>
       <c r="O43" s="18">
         <v>1618</v>
       </c>
@@ -19569,15 +19567,15 @@
       </c>
     </row>
     <row r="44" spans="1:22" s="31" customFormat="1" ht="16.5">
-      <c r="A44" s="194"/>
+      <c r="A44" s="185"/>
       <c r="B44" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="C44" s="82">
+      <c r="C44" s="147">
         <f>SUM(Sheet1!F86,Sheet1!H86,Sheet1!J86,Sheet1!L86,Sheet1!N86,Sheet1!P86)/6</f>
         <v>0</v>
       </c>
-      <c r="D44" s="84"/>
+      <c r="D44" s="149"/>
       <c r="E44" s="60" t="s">
         <v>156</v>
       </c>
@@ -19592,19 +19590,19 @@
         <f>SUM(Sheet1!F91,Sheet1!H91,Sheet1!J91,Sheet1!L91,Sheet1!N91,Sheet1!P91)/6</f>
         <v>0</v>
       </c>
-      <c r="I44" s="148" t="s">
+      <c r="I44" s="97" t="s">
         <v>132</v>
       </c>
       <c r="J44" s="61">
         <v>1603</v>
       </c>
       <c r="K44" s="62"/>
-      <c r="L44" s="184"/>
-      <c r="M44" s="110" t="s">
+      <c r="L44" s="197"/>
+      <c r="M44" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="N44" s="111"/>
-      <c r="O44" s="112"/>
+      <c r="N44" s="129"/>
+      <c r="O44" s="130"/>
       <c r="P44" s="28" t="s">
         <v>117</v>
       </c>
@@ -19634,15 +19632,15 @@
       </c>
     </row>
     <row r="45" spans="1:22" s="31" customFormat="1" ht="16.5">
-      <c r="A45" s="194"/>
+      <c r="A45" s="185"/>
       <c r="B45" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C45" s="82">
+      <c r="C45" s="147">
         <f>SUM(Sheet1!F87,Sheet1!H87,Sheet1!J87,Sheet1!L87,Sheet1!N87,Sheet1!P87)/6</f>
         <v>0</v>
       </c>
-      <c r="D45" s="84"/>
+      <c r="D45" s="149"/>
       <c r="E45" s="63" t="s">
         <v>123</v>
       </c>
@@ -19657,17 +19655,17 @@
         <f>SUM(Sheet1!F92,Sheet1!H92,Sheet1!J92,Sheet1!L92,Sheet1!N92,Sheet1!P92)/6</f>
         <v>0</v>
       </c>
-      <c r="I45" s="149"/>
+      <c r="I45" s="98"/>
       <c r="J45" s="61">
         <v>1608</v>
       </c>
       <c r="K45" s="62"/>
-      <c r="L45" s="184"/>
-      <c r="M45" s="110" t="s">
+      <c r="L45" s="197"/>
+      <c r="M45" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="N45" s="111"/>
-      <c r="O45" s="112"/>
+      <c r="N45" s="129"/>
+      <c r="O45" s="130"/>
       <c r="P45" s="28" t="s">
         <v>118</v>
       </c>
@@ -19697,15 +19695,15 @@
       </c>
     </row>
     <row r="46" spans="1:22" s="31" customFormat="1" ht="16.5">
-      <c r="A46" s="194"/>
+      <c r="A46" s="185"/>
       <c r="B46" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="82">
+      <c r="C46" s="147">
         <f>SUM(Sheet1!F88,Sheet1!H88,Sheet1!J88,Sheet1!L88,Sheet1!N88,Sheet1!P88)/6</f>
         <v>0</v>
       </c>
-      <c r="D46" s="84"/>
+      <c r="D46" s="149"/>
       <c r="E46" s="60" t="s">
         <v>124</v>
       </c>
@@ -19720,17 +19718,17 @@
         <f>SUM(Sheet1!F93,Sheet1!H93,Sheet1!J93,Sheet1!L93,Sheet1!N93,Sheet1!P93)/6</f>
         <v>0</v>
       </c>
-      <c r="I46" s="149"/>
+      <c r="I46" s="98"/>
       <c r="J46" s="61">
         <v>1613</v>
       </c>
       <c r="K46" s="62"/>
-      <c r="L46" s="184"/>
-      <c r="M46" s="110" t="s">
+      <c r="L46" s="197"/>
+      <c r="M46" s="128" t="s">
         <v>157</v>
       </c>
-      <c r="N46" s="111"/>
-      <c r="O46" s="112"/>
+      <c r="N46" s="129"/>
+      <c r="O46" s="130"/>
       <c r="P46" s="28" t="s">
         <v>119</v>
       </c>
@@ -19760,15 +19758,15 @@
       </c>
     </row>
     <row r="47" spans="1:22" s="31" customFormat="1" ht="16.5">
-      <c r="A47" s="194"/>
+      <c r="A47" s="185"/>
       <c r="B47" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C47" s="82">
+      <c r="C47" s="147">
         <f>SUM(Sheet1!F89,Sheet1!H89,Sheet1!J89,Sheet1!L89,Sheet1!N89,Sheet1!P89)/6</f>
         <v>0</v>
       </c>
-      <c r="D47" s="84"/>
+      <c r="D47" s="149"/>
       <c r="E47" s="60" t="s">
         <v>125</v>
       </c>
@@ -19781,19 +19779,19 @@
       </c>
       <c r="H47" s="59">
         <f>SUM(Sheet1!F94,Sheet1!H94,Sheet1!J94,Sheet1!L94,Sheet1!N94,Sheet1!P94)/6</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="I47" s="149"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="98"/>
       <c r="J47" s="64">
         <v>1618</v>
       </c>
       <c r="K47" s="65"/>
-      <c r="L47" s="185"/>
-      <c r="M47" s="110" t="s">
+      <c r="L47" s="198"/>
+      <c r="M47" s="128" t="s">
         <v>158</v>
       </c>
-      <c r="N47" s="111"/>
-      <c r="O47" s="112"/>
+      <c r="N47" s="129"/>
+      <c r="O47" s="130"/>
       <c r="P47" s="28" t="s">
         <v>120</v>
       </c>
@@ -19823,130 +19821,130 @@
       </c>
     </row>
     <row r="48" spans="1:22" s="11" customFormat="1" ht="16.5">
-      <c r="A48" s="98" t="s">
+      <c r="A48" s="134" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="99"/>
-      <c r="C48" s="100"/>
+      <c r="B48" s="135"/>
+      <c r="C48" s="136"/>
       <c r="D48" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E48" s="12"/>
-      <c r="F48" s="95" t="s">
+      <c r="F48" s="131" t="s">
         <v>138</v>
       </c>
-      <c r="G48" s="96"/>
-      <c r="H48" s="96"/>
-      <c r="I48" s="96"/>
-      <c r="J48" s="96"/>
-      <c r="K48" s="96"/>
-      <c r="L48" s="97"/>
-      <c r="M48" s="191" t="s">
+      <c r="G48" s="132"/>
+      <c r="H48" s="132"/>
+      <c r="I48" s="132"/>
+      <c r="J48" s="132"/>
+      <c r="K48" s="132"/>
+      <c r="L48" s="133"/>
+      <c r="M48" s="182" t="s">
         <v>139</v>
       </c>
-      <c r="N48" s="192"/>
-      <c r="O48" s="193"/>
-      <c r="P48" s="189" t="s">
+      <c r="N48" s="183"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="180" t="s">
         <v>140</v>
       </c>
-      <c r="Q48" s="190"/>
-      <c r="R48" s="190"/>
-      <c r="S48" s="190"/>
-      <c r="T48" s="190"/>
-      <c r="U48" s="190"/>
-      <c r="V48" s="190"/>
+      <c r="Q48" s="181"/>
+      <c r="R48" s="181"/>
+      <c r="S48" s="181"/>
+      <c r="T48" s="181"/>
+      <c r="U48" s="181"/>
+      <c r="V48" s="181"/>
     </row>
     <row r="49" spans="1:22" s="11" customFormat="1" ht="16.5">
-      <c r="A49" s="101"/>
-      <c r="B49" s="102"/>
-      <c r="C49" s="103"/>
+      <c r="A49" s="137"/>
+      <c r="B49" s="138"/>
+      <c r="C49" s="139"/>
       <c r="D49" s="12" t="s">
         <v>141</v>
       </c>
       <c r="E49" s="12"/>
-      <c r="F49" s="95" t="s">
+      <c r="F49" s="131" t="s">
         <v>142</v>
       </c>
-      <c r="G49" s="96"/>
-      <c r="H49" s="96"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="96"/>
-      <c r="K49" s="96"/>
-      <c r="L49" s="97"/>
-      <c r="M49" s="88"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="90"/>
-      <c r="P49" s="189" t="s">
+      <c r="G49" s="132"/>
+      <c r="H49" s="132"/>
+      <c r="I49" s="132"/>
+      <c r="J49" s="132"/>
+      <c r="K49" s="132"/>
+      <c r="L49" s="133"/>
+      <c r="M49" s="153"/>
+      <c r="N49" s="154"/>
+      <c r="O49" s="155"/>
+      <c r="P49" s="180" t="s">
         <v>143</v>
       </c>
-      <c r="Q49" s="190"/>
-      <c r="R49" s="190"/>
-      <c r="S49" s="190"/>
-      <c r="T49" s="190"/>
-      <c r="U49" s="190"/>
-      <c r="V49" s="190"/>
+      <c r="Q49" s="181"/>
+      <c r="R49" s="181"/>
+      <c r="S49" s="181"/>
+      <c r="T49" s="181"/>
+      <c r="U49" s="181"/>
+      <c r="V49" s="181"/>
     </row>
     <row r="50" spans="1:22" s="32" customFormat="1" ht="16.5">
-      <c r="A50" s="101"/>
-      <c r="B50" s="102"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="95" t="s">
+      <c r="A50" s="137"/>
+      <c r="B50" s="138"/>
+      <c r="C50" s="139"/>
+      <c r="D50" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="E50" s="97"/>
-      <c r="F50" s="181">
+      <c r="E50" s="133"/>
+      <c r="F50" s="194">
         <f>SUM(Sheet1!F99,Sheet1!H99,Sheet1!J99,Sheet1!L99,Sheet1!N99,Sheet1!P99)/6</f>
         <v>0</v>
       </c>
-      <c r="G50" s="182"/>
-      <c r="H50" s="182"/>
-      <c r="I50" s="182"/>
-      <c r="J50" s="182"/>
-      <c r="K50" s="182"/>
-      <c r="L50" s="183"/>
-      <c r="M50" s="88"/>
-      <c r="N50" s="89"/>
-      <c r="O50" s="90"/>
-      <c r="P50" s="189" t="s">
+      <c r="G50" s="195"/>
+      <c r="H50" s="195"/>
+      <c r="I50" s="195"/>
+      <c r="J50" s="195"/>
+      <c r="K50" s="195"/>
+      <c r="L50" s="196"/>
+      <c r="M50" s="153"/>
+      <c r="N50" s="154"/>
+      <c r="O50" s="155"/>
+      <c r="P50" s="180" t="s">
         <v>144</v>
       </c>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="190"/>
-      <c r="T50" s="190"/>
-      <c r="U50" s="190"/>
-      <c r="V50" s="190"/>
+      <c r="Q50" s="181"/>
+      <c r="R50" s="181"/>
+      <c r="S50" s="181"/>
+      <c r="T50" s="181"/>
+      <c r="U50" s="181"/>
+      <c r="V50" s="181"/>
     </row>
     <row r="51" spans="1:22" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="104"/>
-      <c r="B51" s="105"/>
-      <c r="C51" s="106"/>
-      <c r="D51" s="95" t="s">
+      <c r="A51" s="140"/>
+      <c r="B51" s="141"/>
+      <c r="C51" s="142"/>
+      <c r="D51" s="131" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="97"/>
-      <c r="F51" s="181">
+      <c r="E51" s="133"/>
+      <c r="F51" s="194">
         <f>SUM(Sheet1!F100,Sheet1!H100,Sheet1!J100,Sheet1!L100,Sheet1!N100,Sheet1!P100)/6</f>
         <v>0</v>
       </c>
-      <c r="G51" s="182"/>
-      <c r="H51" s="182"/>
-      <c r="I51" s="182"/>
-      <c r="J51" s="182"/>
-      <c r="K51" s="182"/>
-      <c r="L51" s="183"/>
-      <c r="M51" s="91"/>
-      <c r="N51" s="92"/>
-      <c r="O51" s="93"/>
-      <c r="P51" s="189" t="s">
+      <c r="G51" s="195"/>
+      <c r="H51" s="195"/>
+      <c r="I51" s="195"/>
+      <c r="J51" s="195"/>
+      <c r="K51" s="195"/>
+      <c r="L51" s="196"/>
+      <c r="M51" s="156"/>
+      <c r="N51" s="157"/>
+      <c r="O51" s="158"/>
+      <c r="P51" s="180" t="s">
         <v>145</v>
       </c>
-      <c r="Q51" s="190"/>
-      <c r="R51" s="190"/>
-      <c r="S51" s="190"/>
-      <c r="T51" s="190"/>
-      <c r="U51" s="190"/>
-      <c r="V51" s="190"/>
+      <c r="Q51" s="181"/>
+      <c r="R51" s="181"/>
+      <c r="S51" s="181"/>
+      <c r="T51" s="181"/>
+      <c r="U51" s="181"/>
+      <c r="V51" s="181"/>
     </row>
     <row r="52" spans="1:22" s="11" customFormat="1" ht="16.5">
       <c r="A52" s="34"/>
@@ -20024,6 +20022,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F50:L50"/>
+    <mergeCell ref="F51:L51"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="L26:L47"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="A7:A40"/>
+    <mergeCell ref="B7:D10"/>
+    <mergeCell ref="B14:D19"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="B11:D13"/>
+    <mergeCell ref="B35:C37"/>
+    <mergeCell ref="B20:D27"/>
+    <mergeCell ref="B28:D29"/>
+    <mergeCell ref="B30:D33"/>
+    <mergeCell ref="G3:V3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="G5:V5"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="L7:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:N39"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="M40:N43"/>
     <mergeCell ref="P51:V51"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="M47:O47"/>
@@ -20040,63 +20095,6 @@
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="M44:O44"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:N39"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="M40:N43"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="L7:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="G3:V3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="G5:V5"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="A7:A40"/>
-    <mergeCell ref="B7:D10"/>
-    <mergeCell ref="B14:D19"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="I44:I47"/>
-    <mergeCell ref="B11:D13"/>
-    <mergeCell ref="B35:C37"/>
-    <mergeCell ref="B20:D27"/>
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="B30:D33"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F50:L50"/>
-    <mergeCell ref="F51:L51"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="L26:L47"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="M32:O32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -20142,22 +20140,22 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="126"/>
-      <c r="U3" s="126"/>
-      <c r="V3" s="126"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="121"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="121"/>
+      <c r="U3" s="121"/>
+      <c r="V3" s="121"/>
     </row>
     <row r="4" spans="1:223" ht="22.5">
       <c r="A4" s="8"/>
@@ -20165,19 +20163,19 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="127" t="s">
+      <c r="F4" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="127"/>
-      <c r="P4" s="127"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
@@ -20192,33 +20190,33 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="128"/>
-      <c r="N5" s="128"/>
-      <c r="O5" s="128"/>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="128"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="128"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
     </row>
     <row r="6" spans="1:223" s="17" customFormat="1" ht="33">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="130" t="s">
+      <c r="B6" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="132"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
       <c r="F6" s="10" t="s">
         <v>146</v>
       </c>
@@ -20240,12 +20238,12 @@
       <c r="L6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="130" t="s">
+      <c r="M6" s="125" t="s">
         <v>152</v>
       </c>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="132"/>
+      <c r="N6" s="126"/>
+      <c r="O6" s="126"/>
+      <c r="P6" s="127"/>
       <c r="Q6" s="10" t="s">
         <v>146</v>
       </c>
@@ -20266,14 +20264,14 @@
       </c>
     </row>
     <row r="7" spans="1:223" s="1" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="100" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="135"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="103"/>
       <c r="E7" s="18">
         <v>5404</v>
       </c>
@@ -20301,14 +20299,14 @@
         <f>Sheet1!AB7</f>
         <v>0</v>
       </c>
-      <c r="L7" s="204" t="s">
+      <c r="L7" s="199" t="s">
         <v>47</v>
       </c>
-      <c r="M7" s="118" t="s">
+      <c r="M7" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
       <c r="P7" s="30" t="s">
         <v>49</v>
       </c>
@@ -20539,10 +20537,10 @@
       <c r="HO7" s="3"/>
     </row>
     <row r="8" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A8" s="94"/>
-      <c r="B8" s="139"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="141"/>
+      <c r="A8" s="100"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
       <c r="E8" s="18">
         <v>5408</v>
       </c>
@@ -20570,12 +20568,12 @@
         <f>Sheet1!AB8</f>
         <v>0</v>
       </c>
-      <c r="L8" s="184"/>
-      <c r="M8" s="118" t="s">
+      <c r="L8" s="197"/>
+      <c r="M8" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
       <c r="P8" s="30" t="s">
         <v>51</v>
       </c>
@@ -20605,10 +20603,10 @@
       </c>
     </row>
     <row r="9" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A9" s="94"/>
-      <c r="B9" s="139"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="141"/>
+      <c r="A9" s="100"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="106"/>
       <c r="E9" s="18">
         <v>5414</v>
       </c>
@@ -20636,12 +20634,12 @@
         <f>Sheet1!AB9</f>
         <v>0</v>
       </c>
-      <c r="L9" s="184"/>
-      <c r="M9" s="118" t="s">
+      <c r="L9" s="197"/>
+      <c r="M9" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="110"/>
       <c r="P9" s="30" t="s">
         <v>53</v>
       </c>
@@ -20671,10 +20669,10 @@
       </c>
     </row>
     <row r="10" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A10" s="94"/>
-      <c r="B10" s="136"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="138"/>
+      <c r="A10" s="100"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="109"/>
       <c r="E10" s="18">
         <v>5418</v>
       </c>
@@ -20702,12 +20700,12 @@
         <f>Sheet1!AB10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="184"/>
-      <c r="M10" s="118" t="s">
+      <c r="L10" s="197"/>
+      <c r="M10" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="125"/>
-      <c r="O10" s="125"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
       <c r="P10" s="30" t="s">
         <v>55</v>
       </c>
@@ -20737,12 +20735,12 @@
       </c>
     </row>
     <row r="11" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A11" s="94"/>
-      <c r="B11" s="133" t="s">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="135"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="103"/>
       <c r="E11" s="18">
         <v>4405</v>
       </c>
@@ -20770,12 +20768,12 @@
         <f>Sheet1!AB11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="184"/>
-      <c r="M11" s="118" t="s">
+      <c r="L11" s="197"/>
+      <c r="M11" s="119" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="125"/>
-      <c r="O11" s="125"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="110"/>
       <c r="P11" s="30" t="s">
         <v>57</v>
       </c>
@@ -20805,10 +20803,10 @@
       </c>
     </row>
     <row r="12" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A12" s="94"/>
-      <c r="B12" s="139"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="141"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="18">
         <v>4412</v>
       </c>
@@ -20836,12 +20834,12 @@
         <f>Sheet1!AB12</f>
         <v>0</v>
       </c>
-      <c r="L12" s="184"/>
-      <c r="M12" s="118" t="s">
+      <c r="L12" s="197"/>
+      <c r="M12" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="N12" s="125"/>
-      <c r="O12" s="125"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="110"/>
       <c r="P12" s="30" t="s">
         <v>59</v>
       </c>
@@ -20871,10 +20869,10 @@
       </c>
     </row>
     <row r="13" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A13" s="94"/>
-      <c r="B13" s="136"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="138"/>
+      <c r="A13" s="100"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
       <c r="E13" s="18">
         <v>4420</v>
       </c>
@@ -20902,12 +20900,12 @@
         <f>Sheet1!AB13</f>
         <v>0</v>
       </c>
-      <c r="L13" s="184"/>
-      <c r="M13" s="118" t="s">
+      <c r="L13" s="197"/>
+      <c r="M13" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="125"/>
-      <c r="O13" s="125"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="110"/>
       <c r="P13" s="30" t="s">
         <v>61</v>
       </c>
@@ -20937,12 +20935,12 @@
       </c>
     </row>
     <row r="14" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A14" s="94"/>
-      <c r="B14" s="133" t="s">
+      <c r="A14" s="100"/>
+      <c r="B14" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="135"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="103"/>
       <c r="E14" s="18">
         <v>4402</v>
       </c>
@@ -20970,12 +20968,12 @@
         <f>Sheet1!AB14</f>
         <v>0</v>
       </c>
-      <c r="L14" s="184"/>
-      <c r="M14" s="118" t="s">
+      <c r="L14" s="197"/>
+      <c r="M14" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="110"/>
       <c r="P14" s="30" t="s">
         <v>63</v>
       </c>
@@ -21005,10 +21003,10 @@
       </c>
     </row>
     <row r="15" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A15" s="94"/>
-      <c r="B15" s="139"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="141"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="18">
         <v>4405</v>
       </c>
@@ -21036,12 +21034,12 @@
         <f>Sheet1!AB15</f>
         <v>0</v>
       </c>
-      <c r="L15" s="184"/>
-      <c r="M15" s="118" t="s">
+      <c r="L15" s="197"/>
+      <c r="M15" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="110"/>
       <c r="P15" s="30" t="s">
         <v>65</v>
       </c>
@@ -21071,10 +21069,10 @@
       </c>
     </row>
     <row r="16" spans="1:223" s="2" customFormat="1" ht="16.5">
-      <c r="A16" s="94"/>
-      <c r="B16" s="139"/>
-      <c r="C16" s="140"/>
-      <c r="D16" s="141"/>
+      <c r="A16" s="100"/>
+      <c r="B16" s="104"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="106"/>
       <c r="E16" s="18">
         <v>4409</v>
       </c>
@@ -21102,12 +21100,12 @@
         <f>Sheet1!AB16</f>
         <v>0</v>
       </c>
-      <c r="L16" s="184"/>
-      <c r="M16" s="118" t="s">
+      <c r="L16" s="197"/>
+      <c r="M16" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="N16" s="125"/>
-      <c r="O16" s="125"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
       <c r="P16" s="30" t="s">
         <v>67</v>
       </c>
@@ -21137,10 +21135,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A17" s="94"/>
-      <c r="B17" s="139"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="141"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="104"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="106"/>
       <c r="E17" s="18">
         <v>4412</v>
       </c>
@@ -21168,12 +21166,12 @@
         <f>Sheet1!AB17</f>
         <v>0</v>
       </c>
-      <c r="L17" s="184"/>
-      <c r="M17" s="118" t="s">
+      <c r="L17" s="197"/>
+      <c r="M17" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="N17" s="125"/>
-      <c r="O17" s="125"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="110"/>
       <c r="P17" s="30" t="s">
         <v>69</v>
       </c>
@@ -21203,10 +21201,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A18" s="94"/>
-      <c r="B18" s="139"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="141"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="104"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="106"/>
       <c r="E18" s="18">
         <v>4415</v>
       </c>
@@ -21234,12 +21232,12 @@
         <f>Sheet1!AB18</f>
         <v>0</v>
       </c>
-      <c r="L18" s="184"/>
-      <c r="M18" s="118" t="s">
+      <c r="L18" s="197"/>
+      <c r="M18" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="N18" s="125"/>
-      <c r="O18" s="125"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
       <c r="P18" s="30" t="s">
         <v>71</v>
       </c>
@@ -21269,10 +21267,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A19" s="94"/>
-      <c r="B19" s="139"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="141"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="26">
         <v>4419</v>
       </c>
@@ -21300,12 +21298,12 @@
         <f>Sheet1!AB19</f>
         <v>0</v>
       </c>
-      <c r="L19" s="184"/>
-      <c r="M19" s="118" t="s">
+      <c r="L19" s="197"/>
+      <c r="M19" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="N19" s="125"/>
-      <c r="O19" s="125"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="110"/>
       <c r="P19" s="28" t="s">
         <v>73</v>
       </c>
@@ -21335,12 +21333,12 @@
       </c>
     </row>
     <row r="20" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A20" s="94"/>
-      <c r="B20" s="133" t="s">
+      <c r="A20" s="100"/>
+      <c r="B20" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="134"/>
-      <c r="D20" s="135"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="103"/>
       <c r="E20" s="18">
         <v>3201</v>
       </c>
@@ -21368,12 +21366,12 @@
         <f>Sheet1!AB20</f>
         <v>0</v>
       </c>
-      <c r="L20" s="184"/>
-      <c r="M20" s="118" t="s">
+      <c r="L20" s="197"/>
+      <c r="M20" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="N20" s="125"/>
-      <c r="O20" s="125"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="110"/>
       <c r="P20" s="30" t="s">
         <v>75</v>
       </c>
@@ -21403,10 +21401,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A21" s="94"/>
-      <c r="B21" s="139"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="141"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="106"/>
       <c r="E21" s="18">
         <v>3203</v>
       </c>
@@ -21434,12 +21432,12 @@
         <f>Sheet1!AB21</f>
         <v>0</v>
       </c>
-      <c r="L21" s="184"/>
-      <c r="M21" s="118" t="s">
+      <c r="L21" s="197"/>
+      <c r="M21" s="119" t="s">
         <v>76</v>
       </c>
-      <c r="N21" s="125"/>
-      <c r="O21" s="125"/>
+      <c r="N21" s="110"/>
+      <c r="O21" s="110"/>
       <c r="P21" s="30" t="s">
         <v>77</v>
       </c>
@@ -21469,10 +21467,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A22" s="94"/>
-      <c r="B22" s="139"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="141"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="104"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="106"/>
       <c r="E22" s="17">
         <v>3206</v>
       </c>
@@ -21500,12 +21498,12 @@
         <f>Sheet1!AB22</f>
         <v>0</v>
       </c>
-      <c r="L22" s="184"/>
-      <c r="M22" s="118" t="s">
+      <c r="L22" s="197"/>
+      <c r="M22" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="N22" s="125"/>
-      <c r="O22" s="125"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="110"/>
       <c r="P22" s="30" t="s">
         <v>79</v>
       </c>
@@ -21535,10 +21533,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A23" s="94"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="106"/>
       <c r="E23" s="18">
         <v>3208</v>
       </c>
@@ -21566,12 +21564,12 @@
         <f>Sheet1!AB23</f>
         <v>0</v>
       </c>
-      <c r="L23" s="184"/>
-      <c r="M23" s="118" t="s">
+      <c r="L23" s="197"/>
+      <c r="M23" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="N23" s="125"/>
-      <c r="O23" s="125"/>
+      <c r="N23" s="110"/>
+      <c r="O23" s="110"/>
       <c r="P23" s="17" t="s">
         <v>81</v>
       </c>
@@ -21601,10 +21599,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A24" s="94"/>
-      <c r="B24" s="139"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="141"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="106"/>
       <c r="E24" s="18">
         <v>3211</v>
       </c>
@@ -21632,12 +21630,12 @@
         <f>Sheet1!AB24</f>
         <v>0</v>
       </c>
-      <c r="L24" s="184"/>
-      <c r="M24" s="118" t="s">
+      <c r="L24" s="197"/>
+      <c r="M24" s="119" t="s">
         <v>82</v>
       </c>
-      <c r="N24" s="125"/>
-      <c r="O24" s="125"/>
+      <c r="N24" s="110"/>
+      <c r="O24" s="110"/>
       <c r="P24" s="30" t="s">
         <v>83</v>
       </c>
@@ -21667,10 +21665,10 @@
       </c>
     </row>
     <row r="25" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A25" s="94"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="141"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="106"/>
       <c r="E25" s="18">
         <v>3213</v>
       </c>
@@ -21698,12 +21696,12 @@
         <f>Sheet1!AB25</f>
         <v>0</v>
       </c>
-      <c r="L25" s="185"/>
-      <c r="M25" s="118" t="s">
+      <c r="L25" s="198"/>
+      <c r="M25" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="N25" s="125"/>
-      <c r="O25" s="125"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="110"/>
       <c r="P25" s="30" t="s">
         <v>85</v>
       </c>
@@ -21733,10 +21731,10 @@
       </c>
     </row>
     <row r="26" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A26" s="94"/>
-      <c r="B26" s="139"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="141"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="106"/>
       <c r="E26" s="18">
         <v>3216</v>
       </c>
@@ -21764,14 +21762,14 @@
         <f>Sheet1!AB26</f>
         <v>0</v>
       </c>
-      <c r="L26" s="184" t="s">
+      <c r="L26" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="M26" s="116" t="s">
+      <c r="M26" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="N26" s="117"/>
-      <c r="O26" s="118"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="119"/>
       <c r="P26" s="28" t="s">
         <v>88</v>
       </c>
@@ -21801,10 +21799,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A27" s="94"/>
-      <c r="B27" s="136"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="138"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
       <c r="E27" s="18">
         <v>3218</v>
       </c>
@@ -21832,12 +21830,12 @@
         <f>Sheet1!AB27</f>
         <v>0</v>
       </c>
-      <c r="L27" s="184"/>
-      <c r="M27" s="116" t="s">
+      <c r="L27" s="197"/>
+      <c r="M27" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="N27" s="117"/>
-      <c r="O27" s="118"/>
+      <c r="N27" s="118"/>
+      <c r="O27" s="119"/>
       <c r="P27" s="28" t="s">
         <v>90</v>
       </c>
@@ -21867,12 +21865,12 @@
       </c>
     </row>
     <row r="28" spans="1:22" s="2" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="133" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="134"/>
-      <c r="D28" s="135"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103"/>
       <c r="E28" s="18">
         <v>1808</v>
       </c>
@@ -21900,12 +21898,12 @@
         <f>Sheet1!AB28</f>
         <v>0</v>
       </c>
-      <c r="L28" s="184"/>
-      <c r="M28" s="116" t="s">
+      <c r="L28" s="197"/>
+      <c r="M28" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="N28" s="117"/>
-      <c r="O28" s="118"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="119"/>
       <c r="P28" s="28" t="s">
         <v>92</v>
       </c>
@@ -21935,10 +21933,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A29" s="94"/>
-      <c r="B29" s="136"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="138"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="107"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109"/>
       <c r="E29" s="18">
         <v>1818</v>
       </c>
@@ -21966,12 +21964,12 @@
         <f>Sheet1!AB29</f>
         <v>0</v>
       </c>
-      <c r="L29" s="184"/>
-      <c r="M29" s="116" t="s">
+      <c r="L29" s="197"/>
+      <c r="M29" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="N29" s="117"/>
-      <c r="O29" s="118"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="119"/>
       <c r="P29" s="28" t="s">
         <v>94</v>
       </c>
@@ -22001,12 +21999,12 @@
       </c>
     </row>
     <row r="30" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A30" s="94"/>
-      <c r="B30" s="133" t="s">
+      <c r="A30" s="100"/>
+      <c r="B30" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="135"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
       <c r="E30" s="18">
         <v>1403</v>
       </c>
@@ -22034,12 +22032,12 @@
         <f>Sheet1!AB30</f>
         <v>0</v>
       </c>
-      <c r="L30" s="184"/>
-      <c r="M30" s="116" t="s">
+      <c r="L30" s="197"/>
+      <c r="M30" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="N30" s="117"/>
-      <c r="O30" s="118"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="119"/>
       <c r="P30" s="28" t="s">
         <v>96</v>
       </c>
@@ -22069,10 +22067,10 @@
       </c>
     </row>
     <row r="31" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A31" s="94"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="141"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="106"/>
       <c r="E31" s="18">
         <v>1408</v>
       </c>
@@ -22100,12 +22098,12 @@
         <f>Sheet1!AB31</f>
         <v>0</v>
       </c>
-      <c r="L31" s="184"/>
-      <c r="M31" s="116" t="s">
+      <c r="L31" s="197"/>
+      <c r="M31" s="117" t="s">
         <v>97</v>
       </c>
-      <c r="N31" s="117"/>
-      <c r="O31" s="118"/>
+      <c r="N31" s="118"/>
+      <c r="O31" s="119"/>
       <c r="P31" s="28" t="s">
         <v>98</v>
       </c>
@@ -22135,10 +22133,10 @@
       </c>
     </row>
     <row r="32" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A32" s="94"/>
-      <c r="B32" s="139"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="141"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="106"/>
       <c r="E32" s="18">
         <v>1413</v>
       </c>
@@ -22166,12 +22164,12 @@
         <f>Sheet1!AB32</f>
         <v>0</v>
       </c>
-      <c r="L32" s="184"/>
-      <c r="M32" s="116" t="s">
+      <c r="L32" s="197"/>
+      <c r="M32" s="117" t="s">
         <v>99</v>
       </c>
-      <c r="N32" s="117"/>
-      <c r="O32" s="118"/>
+      <c r="N32" s="118"/>
+      <c r="O32" s="119"/>
       <c r="P32" s="28" t="s">
         <v>100</v>
       </c>
@@ -22201,10 +22199,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A33" s="94"/>
-      <c r="B33" s="136"/>
-      <c r="C33" s="137"/>
-      <c r="D33" s="138"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="109"/>
       <c r="E33" s="18">
         <v>1418</v>
       </c>
@@ -22232,12 +22230,12 @@
         <f>Sheet1!AB33</f>
         <v>0</v>
       </c>
-      <c r="L33" s="184"/>
-      <c r="M33" s="116" t="s">
+      <c r="L33" s="197"/>
+      <c r="M33" s="117" t="s">
         <v>101</v>
       </c>
-      <c r="N33" s="117"/>
-      <c r="O33" s="118"/>
+      <c r="N33" s="118"/>
+      <c r="O33" s="119"/>
       <c r="P33" s="28" t="s">
         <v>102</v>
       </c>
@@ -22267,12 +22265,12 @@
       </c>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A34" s="94"/>
-      <c r="B34" s="145" t="s">
+      <c r="A34" s="100"/>
+      <c r="B34" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="146"/>
-      <c r="D34" s="147"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="96"/>
       <c r="E34" s="18">
         <v>4311</v>
       </c>
@@ -22300,12 +22298,12 @@
         <f>Sheet1!AB34</f>
         <v>0</v>
       </c>
-      <c r="L34" s="184"/>
-      <c r="M34" s="116" t="s">
+      <c r="L34" s="197"/>
+      <c r="M34" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="N34" s="117"/>
-      <c r="O34" s="118"/>
+      <c r="N34" s="118"/>
+      <c r="O34" s="119"/>
       <c r="P34" s="28" t="s">
         <v>104</v>
       </c>
@@ -22335,11 +22333,11 @@
       </c>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A35" s="94"/>
-      <c r="B35" s="119" t="s">
+      <c r="A35" s="100"/>
+      <c r="B35" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="120"/>
+      <c r="C35" s="112"/>
       <c r="D35" s="13" t="s">
         <v>38</v>
       </c>
@@ -22368,12 +22366,12 @@
         <f>Sheet1!AB35</f>
         <v>0</v>
       </c>
-      <c r="L35" s="184"/>
-      <c r="M35" s="116" t="s">
+      <c r="L35" s="197"/>
+      <c r="M35" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="N35" s="117"/>
-      <c r="O35" s="118"/>
+      <c r="N35" s="118"/>
+      <c r="O35" s="119"/>
       <c r="P35" s="28" t="s">
         <v>106</v>
       </c>
@@ -22403,9 +22401,9 @@
       </c>
     </row>
     <row r="36" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A36" s="94"/>
-      <c r="B36" s="121"/>
-      <c r="C36" s="122"/>
+      <c r="A36" s="100"/>
+      <c r="B36" s="113"/>
+      <c r="C36" s="114"/>
       <c r="D36" s="13" t="s">
         <v>39</v>
       </c>
@@ -22434,11 +22432,11 @@
         <f>Sheet1!AB36</f>
         <v>0</v>
       </c>
-      <c r="L36" s="184"/>
-      <c r="M36" s="119" t="s">
+      <c r="L36" s="197"/>
+      <c r="M36" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="N36" s="120"/>
+      <c r="N36" s="112"/>
       <c r="O36" s="18">
         <v>1603</v>
       </c>
@@ -22471,9 +22469,9 @@
       </c>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A37" s="94"/>
-      <c r="B37" s="123"/>
-      <c r="C37" s="124"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="13" t="s">
         <v>40</v>
       </c>
@@ -22502,9 +22500,9 @@
         <f>Sheet1!AB37</f>
         <v>0</v>
       </c>
-      <c r="L37" s="184"/>
-      <c r="M37" s="121"/>
-      <c r="N37" s="122"/>
+      <c r="L37" s="197"/>
+      <c r="M37" s="113"/>
+      <c r="N37" s="114"/>
       <c r="O37" s="18">
         <v>1608</v>
       </c>
@@ -22537,12 +22535,12 @@
       </c>
     </row>
     <row r="38" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A38" s="94"/>
-      <c r="B38" s="116" t="s">
+      <c r="A38" s="100"/>
+      <c r="B38" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="117"/>
-      <c r="D38" s="118"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
       <c r="E38" s="18"/>
       <c r="F38" s="25">
         <f>Sheet1!R38</f>
@@ -22568,9 +22566,9 @@
         <f>Sheet1!AB38</f>
         <v>0</v>
       </c>
-      <c r="L38" s="184"/>
-      <c r="M38" s="121"/>
-      <c r="N38" s="122"/>
+      <c r="L38" s="197"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="114"/>
       <c r="O38" s="18">
         <v>1613</v>
       </c>
@@ -22603,11 +22601,11 @@
       </c>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A39" s="94"/>
-      <c r="B39" s="125" t="s">
+      <c r="A39" s="100"/>
+      <c r="B39" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="125"/>
+      <c r="C39" s="110"/>
       <c r="D39" s="15" t="s">
         <v>43</v>
       </c>
@@ -22638,9 +22636,9 @@
         <f>Sheet1!AB39</f>
         <v>0</v>
       </c>
-      <c r="L39" s="184"/>
-      <c r="M39" s="123"/>
-      <c r="N39" s="124"/>
+      <c r="L39" s="197"/>
+      <c r="M39" s="115"/>
+      <c r="N39" s="116"/>
       <c r="O39" s="18">
         <v>1618</v>
       </c>
@@ -22673,9 +22671,9 @@
       </c>
     </row>
     <row r="40" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A40" s="94"/>
-      <c r="B40" s="125"/>
-      <c r="C40" s="125"/>
+      <c r="A40" s="100"/>
+      <c r="B40" s="110"/>
+      <c r="C40" s="110"/>
       <c r="D40" s="15" t="s">
         <v>45</v>
       </c>
@@ -22706,11 +22704,11 @@
         <f>Sheet1!AB40</f>
         <v>0</v>
       </c>
-      <c r="L40" s="184"/>
-      <c r="M40" s="119" t="s">
+      <c r="L40" s="197"/>
+      <c r="M40" s="111" t="s">
         <v>112</v>
       </c>
-      <c r="N40" s="120"/>
+      <c r="N40" s="112"/>
       <c r="O40" s="18">
         <v>1603</v>
       </c>
@@ -22743,10 +22741,10 @@
       </c>
     </row>
     <row r="41" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A41" s="94" t="s">
+      <c r="A41" s="100" t="s">
         <v>154</v>
       </c>
-      <c r="B41" s="119" t="s">
+      <c r="B41" s="111" t="s">
         <v>155</v>
       </c>
       <c r="C41" s="200"/>
@@ -22760,9 +22758,9 @@
       <c r="I41" s="203"/>
       <c r="J41" s="203"/>
       <c r="K41" s="203"/>
-      <c r="L41" s="184"/>
-      <c r="M41" s="121"/>
-      <c r="N41" s="122"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="113"/>
+      <c r="N41" s="114"/>
       <c r="O41" s="18">
         <v>1608</v>
       </c>
@@ -22795,8 +22793,8 @@
       </c>
     </row>
     <row r="42" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A42" s="94"/>
-      <c r="B42" s="121"/>
+      <c r="A42" s="100"/>
+      <c r="B42" s="113"/>
       <c r="C42" s="201"/>
       <c r="D42" s="201"/>
       <c r="E42" s="201"/>
@@ -22806,9 +22804,9 @@
       <c r="I42" s="203"/>
       <c r="J42" s="203"/>
       <c r="K42" s="203"/>
-      <c r="L42" s="184"/>
-      <c r="M42" s="121"/>
-      <c r="N42" s="122"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="113"/>
+      <c r="N42" s="114"/>
       <c r="O42" s="18">
         <v>1613</v>
       </c>
@@ -22841,8 +22839,8 @@
       </c>
     </row>
     <row r="43" spans="1:22" s="2" customFormat="1" ht="16.5">
-      <c r="A43" s="94"/>
-      <c r="B43" s="123"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="115"/>
       <c r="C43" s="202"/>
       <c r="D43" s="202"/>
       <c r="E43" s="202"/>
@@ -22852,9 +22850,9 @@
       <c r="I43" s="203"/>
       <c r="J43" s="203"/>
       <c r="K43" s="203"/>
-      <c r="L43" s="184"/>
-      <c r="M43" s="123"/>
-      <c r="N43" s="124"/>
+      <c r="L43" s="197"/>
+      <c r="M43" s="115"/>
+      <c r="N43" s="116"/>
       <c r="O43" s="18">
         <v>1618</v>
       </c>
@@ -22887,15 +22885,15 @@
       </c>
     </row>
     <row r="44" spans="1:22" s="31" customFormat="1" ht="16.5">
-      <c r="A44" s="94"/>
+      <c r="A44" s="100"/>
       <c r="B44" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="C44" s="82">
+      <c r="C44" s="147">
         <f>SUM(Sheet1!R86,Sheet1!T86,Sheet1!V86,Sheet1!X86,Sheet1!Z86,Sheet1!AB86)/6</f>
         <v>0</v>
       </c>
-      <c r="D44" s="84"/>
+      <c r="D44" s="149"/>
       <c r="E44" s="60" t="s">
         <v>156</v>
       </c>
@@ -22910,19 +22908,19 @@
         <f>SUM(Sheet1!R91,Sheet1!T91,Sheet1!V91,Sheet1!X91,Sheet1!Z91,Sheet1!AB91)/6</f>
         <v>0</v>
       </c>
-      <c r="I44" s="148" t="s">
+      <c r="I44" s="97" t="s">
         <v>132</v>
       </c>
       <c r="J44" s="61">
         <v>1603</v>
       </c>
       <c r="K44" s="66"/>
-      <c r="L44" s="184"/>
-      <c r="M44" s="110" t="s">
+      <c r="L44" s="197"/>
+      <c r="M44" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="N44" s="111"/>
-      <c r="O44" s="112"/>
+      <c r="N44" s="129"/>
+      <c r="O44" s="130"/>
       <c r="P44" s="28" t="s">
         <v>117</v>
       </c>
@@ -22952,15 +22950,15 @@
       </c>
     </row>
     <row r="45" spans="1:22" s="31" customFormat="1" ht="16.5">
-      <c r="A45" s="94"/>
+      <c r="A45" s="100"/>
       <c r="B45" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C45" s="82">
+      <c r="C45" s="147">
         <f>SUM(Sheet1!R87,Sheet1!T87,Sheet1!V87,Sheet1!X87,Sheet1!Z87,Sheet1!AB87)/6</f>
         <v>0</v>
       </c>
-      <c r="D45" s="84"/>
+      <c r="D45" s="149"/>
       <c r="E45" s="63" t="s">
         <v>123</v>
       </c>
@@ -22975,17 +22973,17 @@
         <f>SUM(Sheet1!R92,Sheet1!T92,Sheet1!V92,Sheet1!X92,Sheet1!Z92,Sheet1!AB92)/6</f>
         <v>0</v>
       </c>
-      <c r="I45" s="149"/>
+      <c r="I45" s="98"/>
       <c r="J45" s="61">
         <v>1608</v>
       </c>
       <c r="K45" s="66"/>
-      <c r="L45" s="184"/>
-      <c r="M45" s="110" t="s">
+      <c r="L45" s="197"/>
+      <c r="M45" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="N45" s="111"/>
-      <c r="O45" s="112"/>
+      <c r="N45" s="129"/>
+      <c r="O45" s="130"/>
       <c r="P45" s="28" t="s">
         <v>118</v>
       </c>
@@ -23015,15 +23013,15 @@
       </c>
     </row>
     <row r="46" spans="1:22" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A46" s="94"/>
+      <c r="A46" s="100"/>
       <c r="B46" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="82">
+      <c r="C46" s="147">
         <f>SUM(Sheet1!R88,Sheet1!T88,Sheet1!V88,Sheet1!X88,Sheet1!Z88,Sheet1!AB88)/6</f>
         <v>0</v>
       </c>
-      <c r="D46" s="84"/>
+      <c r="D46" s="149"/>
       <c r="E46" s="60" t="s">
         <v>124</v>
       </c>
@@ -23038,17 +23036,17 @@
         <f>SUM(Sheet1!R93,Sheet1!T93,Sheet1!V93,Sheet1!X93,Sheet1!Z93,Sheet1!AB93)/6</f>
         <v>0</v>
       </c>
-      <c r="I46" s="149"/>
+      <c r="I46" s="98"/>
       <c r="J46" s="61">
         <v>1613</v>
       </c>
       <c r="K46" s="66"/>
-      <c r="L46" s="184"/>
-      <c r="M46" s="110" t="s">
+      <c r="L46" s="197"/>
+      <c r="M46" s="128" t="s">
         <v>157</v>
       </c>
-      <c r="N46" s="111"/>
-      <c r="O46" s="112"/>
+      <c r="N46" s="129"/>
+      <c r="O46" s="130"/>
       <c r="P46" s="28" t="s">
         <v>119</v>
       </c>
@@ -23078,15 +23076,15 @@
       </c>
     </row>
     <row r="47" spans="1:22" s="31" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A47" s="94"/>
+      <c r="A47" s="100"/>
       <c r="B47" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C47" s="82">
+      <c r="C47" s="147">
         <f>SUM(Sheet1!R89,Sheet1!T89,Sheet1!V89,Sheet1!X89,Sheet1!Z89,Sheet1!AB89)/6</f>
         <v>0</v>
       </c>
-      <c r="D47" s="84"/>
+      <c r="D47" s="149"/>
       <c r="E47" s="60" t="s">
         <v>125</v>
       </c>
@@ -23101,17 +23099,17 @@
         <f>SUM(Sheet1!R94,Sheet1!T94,Sheet1!V94,Sheet1!X94,Sheet1!Z94,Sheet1!AB94)/6</f>
         <v>0</v>
       </c>
-      <c r="I47" s="149"/>
+      <c r="I47" s="98"/>
       <c r="J47" s="64">
         <v>1618</v>
       </c>
       <c r="K47" s="65"/>
-      <c r="L47" s="185"/>
-      <c r="M47" s="110" t="s">
+      <c r="L47" s="198"/>
+      <c r="M47" s="128" t="s">
         <v>158</v>
       </c>
-      <c r="N47" s="111"/>
-      <c r="O47" s="112"/>
+      <c r="N47" s="129"/>
+      <c r="O47" s="130"/>
       <c r="P47" s="28" t="s">
         <v>120</v>
       </c>
@@ -23141,130 +23139,130 @@
       </c>
     </row>
     <row r="48" spans="1:22" s="11" customFormat="1" ht="16.5">
-      <c r="A48" s="98" t="s">
+      <c r="A48" s="134" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="99"/>
-      <c r="C48" s="100"/>
+      <c r="B48" s="135"/>
+      <c r="C48" s="136"/>
       <c r="D48" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E48" s="12"/>
-      <c r="F48" s="95" t="s">
+      <c r="F48" s="131" t="s">
         <v>138</v>
       </c>
-      <c r="G48" s="96"/>
-      <c r="H48" s="96"/>
-      <c r="I48" s="96"/>
-      <c r="J48" s="96"/>
-      <c r="K48" s="96"/>
-      <c r="L48" s="97"/>
-      <c r="M48" s="191" t="s">
+      <c r="G48" s="132"/>
+      <c r="H48" s="132"/>
+      <c r="I48" s="132"/>
+      <c r="J48" s="132"/>
+      <c r="K48" s="132"/>
+      <c r="L48" s="133"/>
+      <c r="M48" s="182" t="s">
         <v>139</v>
       </c>
-      <c r="N48" s="192"/>
-      <c r="O48" s="193"/>
-      <c r="P48" s="189" t="s">
+      <c r="N48" s="183"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="180" t="s">
         <v>140</v>
       </c>
-      <c r="Q48" s="190"/>
-      <c r="R48" s="190"/>
-      <c r="S48" s="190"/>
-      <c r="T48" s="190"/>
-      <c r="U48" s="190"/>
-      <c r="V48" s="190"/>
+      <c r="Q48" s="181"/>
+      <c r="R48" s="181"/>
+      <c r="S48" s="181"/>
+      <c r="T48" s="181"/>
+      <c r="U48" s="181"/>
+      <c r="V48" s="181"/>
     </row>
     <row r="49" spans="1:22" s="11" customFormat="1" ht="16.5">
-      <c r="A49" s="101"/>
-      <c r="B49" s="102"/>
-      <c r="C49" s="103"/>
+      <c r="A49" s="137"/>
+      <c r="B49" s="138"/>
+      <c r="C49" s="139"/>
       <c r="D49" s="12" t="s">
         <v>141</v>
       </c>
       <c r="E49" s="12"/>
-      <c r="F49" s="95" t="s">
+      <c r="F49" s="131" t="s">
         <v>142</v>
       </c>
-      <c r="G49" s="96"/>
-      <c r="H49" s="96"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="96"/>
-      <c r="K49" s="96"/>
-      <c r="L49" s="97"/>
-      <c r="M49" s="88"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="90"/>
-      <c r="P49" s="189" t="s">
+      <c r="G49" s="132"/>
+      <c r="H49" s="132"/>
+      <c r="I49" s="132"/>
+      <c r="J49" s="132"/>
+      <c r="K49" s="132"/>
+      <c r="L49" s="133"/>
+      <c r="M49" s="153"/>
+      <c r="N49" s="154"/>
+      <c r="O49" s="155"/>
+      <c r="P49" s="180" t="s">
         <v>143</v>
       </c>
-      <c r="Q49" s="190"/>
-      <c r="R49" s="190"/>
-      <c r="S49" s="190"/>
-      <c r="T49" s="190"/>
-      <c r="U49" s="190"/>
-      <c r="V49" s="190"/>
+      <c r="Q49" s="181"/>
+      <c r="R49" s="181"/>
+      <c r="S49" s="181"/>
+      <c r="T49" s="181"/>
+      <c r="U49" s="181"/>
+      <c r="V49" s="181"/>
     </row>
     <row r="50" spans="1:22" s="32" customFormat="1" ht="16.5">
-      <c r="A50" s="101"/>
-      <c r="B50" s="102"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="95" t="s">
+      <c r="A50" s="137"/>
+      <c r="B50" s="138"/>
+      <c r="C50" s="139"/>
+      <c r="D50" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="E50" s="97"/>
-      <c r="F50" s="182">
+      <c r="E50" s="133"/>
+      <c r="F50" s="195">
         <f>SUM(Sheet1!R99,Sheet1!T99,Sheet1!V99,Sheet1!X99,Sheet1!Z99,Sheet1!AB99)/6</f>
         <v>0</v>
       </c>
-      <c r="G50" s="182"/>
-      <c r="H50" s="182"/>
-      <c r="I50" s="182"/>
-      <c r="J50" s="182"/>
-      <c r="K50" s="182"/>
-      <c r="L50" s="183"/>
-      <c r="M50" s="88"/>
-      <c r="N50" s="89"/>
-      <c r="O50" s="90"/>
-      <c r="P50" s="189" t="s">
+      <c r="G50" s="195"/>
+      <c r="H50" s="195"/>
+      <c r="I50" s="195"/>
+      <c r="J50" s="195"/>
+      <c r="K50" s="195"/>
+      <c r="L50" s="196"/>
+      <c r="M50" s="153"/>
+      <c r="N50" s="154"/>
+      <c r="O50" s="155"/>
+      <c r="P50" s="180" t="s">
         <v>144</v>
       </c>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="190"/>
-      <c r="T50" s="190"/>
-      <c r="U50" s="190"/>
-      <c r="V50" s="190"/>
+      <c r="Q50" s="181"/>
+      <c r="R50" s="181"/>
+      <c r="S50" s="181"/>
+      <c r="T50" s="181"/>
+      <c r="U50" s="181"/>
+      <c r="V50" s="181"/>
     </row>
     <row r="51" spans="1:22" s="33" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A51" s="104"/>
-      <c r="B51" s="105"/>
-      <c r="C51" s="106"/>
-      <c r="D51" s="95" t="s">
+      <c r="A51" s="140"/>
+      <c r="B51" s="141"/>
+      <c r="C51" s="142"/>
+      <c r="D51" s="131" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="97"/>
-      <c r="F51" s="182">
+      <c r="E51" s="133"/>
+      <c r="F51" s="195">
         <f>SUM(Sheet1!R100,Sheet1!T100,Sheet1!V100,Sheet1!X100,Sheet1!Z100,Sheet1!AB100)/6</f>
         <v>0</v>
       </c>
-      <c r="G51" s="182"/>
-      <c r="H51" s="182"/>
-      <c r="I51" s="182"/>
-      <c r="J51" s="182"/>
-      <c r="K51" s="182"/>
-      <c r="L51" s="183"/>
-      <c r="M51" s="91"/>
-      <c r="N51" s="92"/>
-      <c r="O51" s="93"/>
-      <c r="P51" s="189" t="s">
+      <c r="G51" s="195"/>
+      <c r="H51" s="195"/>
+      <c r="I51" s="195"/>
+      <c r="J51" s="195"/>
+      <c r="K51" s="195"/>
+      <c r="L51" s="196"/>
+      <c r="M51" s="156"/>
+      <c r="N51" s="157"/>
+      <c r="O51" s="158"/>
+      <c r="P51" s="180" t="s">
         <v>145</v>
       </c>
-      <c r="Q51" s="190"/>
-      <c r="R51" s="190"/>
-      <c r="S51" s="190"/>
-      <c r="T51" s="190"/>
-      <c r="U51" s="190"/>
-      <c r="V51" s="190"/>
+      <c r="Q51" s="181"/>
+      <c r="R51" s="181"/>
+      <c r="S51" s="181"/>
+      <c r="T51" s="181"/>
+      <c r="U51" s="181"/>
+      <c r="V51" s="181"/>
     </row>
     <row r="52" spans="1:22" s="11" customFormat="1" ht="16.5">
       <c r="A52" s="34"/>
@@ -23342,6 +23340,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="A48:C51"/>
+    <mergeCell ref="F48:L48"/>
+    <mergeCell ref="M48:O51"/>
+    <mergeCell ref="P51:V51"/>
+    <mergeCell ref="F50:L50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:L51"/>
+    <mergeCell ref="P48:V48"/>
+    <mergeCell ref="F49:L49"/>
+    <mergeCell ref="P49:V49"/>
+    <mergeCell ref="P50:V50"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:F43"/>
+    <mergeCell ref="G41:K43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="B35:C37"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:N39"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="M40:N43"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="B20:D27"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="L26:L47"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="B28:D29"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="B30:D33"/>
+    <mergeCell ref="G3:V3"/>
+    <mergeCell ref="F4:P4"/>
+    <mergeCell ref="G5:V5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="M6:P6"/>
     <mergeCell ref="A7:A40"/>
     <mergeCell ref="B7:D10"/>
     <mergeCell ref="L7:L25"/>
@@ -23358,69 +23413,94 @@
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="M16:O16"/>
     <mergeCell ref="M17:O17"/>
-    <mergeCell ref="G3:V3"/>
-    <mergeCell ref="F4:P4"/>
-    <mergeCell ref="G5:V5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="B20:D27"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="L26:L47"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="B30:D33"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="B35:C37"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:N39"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="M40:N43"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:F43"/>
-    <mergeCell ref="G41:K43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="I44:I47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A48:C51"/>
-    <mergeCell ref="F48:L48"/>
-    <mergeCell ref="M48:O51"/>
-    <mergeCell ref="P51:V51"/>
-    <mergeCell ref="F50:L50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:L51"/>
-    <mergeCell ref="P48:V48"/>
-    <mergeCell ref="F49:L49"/>
-    <mergeCell ref="P49:V49"/>
-    <mergeCell ref="P50:V50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <WorkflowStatus xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">Soạn thảo</WorkflowStatus>
+    <WorkflowURL xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">&lt;a href='/workflow/SitePages/Workflow.aspx?mode=2&amp;LID=254ea173-42a4-4b32-afbf-3bf770118a86&amp;itemID=133721' target='_blank'&gt;OS2312121972&lt;/a&gt;</WorkflowURL>
+    <DocumentCategoryData xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
+    <DocumentCategoryID xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">161</DocumentCategoryID>
+    <Abstract xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
+    <WorkflowID xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">132</WorkflowID>
+    <Index xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
+    <DocumentCategory xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">161;#Tài liệu tham khảo</DocumentCategory>
+    <Required xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
+    <RequestCode xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">OS2312121972</RequestCode>
+    <Workflow xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">Quy trình Trình ký online</Workflow>
+    <_dlc_DocId xmlns="998bb92a-6464-419f-a0f9-924a868214cd">DQURWQRM4CD3-1578625852-569709</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="998bb92a-6464-419f-a0f9-924a868214cd">
+      <Url>https://eoffice.hoaphat.com.vn/record23/dungquat/_layouts/15/DocIdRedir.aspx?ID=DQURWQRM4CD3-1578625852-569709</Url>
+      <Description>DQURWQRM4CD3-1578625852-569709</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004E80E4044EF8C64283904840BF522E83" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0cd73694a5f7c96a9bd28f75f6889f88">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="998bb92a-6464-419f-a0f9-924a868214cd" xmlns:ns3="0861895e-72d3-49e1-9fd6-30e326ecfd33" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d17a98453237ee78ca208d86170a4f1" ns2:_="" ns3:_="">
     <xsd:import namespace="998bb92a-6464-419f-a0f9-924a868214cd"/>
@@ -23670,89 +23750,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <WorkflowStatus xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">Soạn thảo</WorkflowStatus>
-    <WorkflowURL xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">&lt;a href='/workflow/SitePages/Workflow.aspx?mode=2&amp;LID=254ea173-42a4-4b32-afbf-3bf770118a86&amp;itemID=133721' target='_blank'&gt;OS2312121972&lt;/a&gt;</WorkflowURL>
-    <DocumentCategoryData xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
-    <DocumentCategoryID xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">161</DocumentCategoryID>
-    <Abstract xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
-    <WorkflowID xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">132</WorkflowID>
-    <Index xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
-    <DocumentCategory xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">161;#Tài liệu tham khảo</DocumentCategory>
-    <Required xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33" xsi:nil="true"/>
-    <RequestCode xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">OS2312121972</RequestCode>
-    <Workflow xmlns="0861895e-72d3-49e1-9fd6-30e326ecfd33">Quy trình Trình ký online</Workflow>
-    <_dlc_DocId xmlns="998bb92a-6464-419f-a0f9-924a868214cd">DQURWQRM4CD3-1578625852-569709</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="998bb92a-6464-419f-a0f9-924a868214cd">
-      <Url>https://eoffice.hoaphat.com.vn/record23/dungquat/_layouts/15/DocIdRedir.aspx?ID=DQURWQRM4CD3-1578625852-569709</Url>
-      <Description>DQURWQRM4CD3-1578625852-569709</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FEED28-00EE-4310-9380-BC6DE9840F9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B898D909-4CB7-4B8E-BF6A-C53B57E30FF4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{352342B9-2286-4254-A508-C505873421E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0861895e-72d3-49e1-9fd6-30e326ecfd33"/>
+    <ds:schemaRef ds:uri="998bb92a-6464-419f-a0f9-924a868214cd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FA947CA-8091-45E6-8549-EEAFAB5613C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23769,31 +23794,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{352342B9-2286-4254-A508-C505873421E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0861895e-72d3-49e1-9fd6-30e326ecfd33"/>
-    <ds:schemaRef ds:uri="998bb92a-6464-419f-a0f9-924a868214cd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B898D909-4CB7-4B8E-BF6A-C53B57E30FF4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FEED28-00EE-4310-9380-BC6DE9840F9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>